--- a/insumos_excel/03- ARQUEOS MF MARZO 2026 (3).xlsx
+++ b/insumos_excel/03- ARQUEOS MF MARZO 2026 (3).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancolombia-my.sharepoint.com/personal/cridia_bancolombia_com_co/Documents/SERVICIOS FINANCIEROS SUCURSALES/ANA CRIS/PLANILLAS DE ARQUEOS MF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\EUC\reglas_multifuncionales\insumos_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2319" documentId="13_ncr:1_{6A0F8E7C-6B68-4F57-9441-FE088613A30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A0465B9-0C68-4653-BE89-8A34AC3A1879}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2456A-9E73-4B0D-B316-4543D22B8D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="455" xr2:uid="{9144873E-EC7E-4C0A-A8AE-476FA54C6A71}"/>
   </bookViews>
@@ -39,9 +39,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -203,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4168" uniqueCount="988">
   <si>
     <t>dispensado_corte_arqueo</t>
   </si>
@@ -3111,18 +3112,131 @@
   <si>
     <t>cruzar faltante $2.700.000 con sob 20260315</t>
   </si>
+  <si>
+    <t xml:space="preserve"> $ -  </t>
+  </si>
+  <si>
+    <t>Sobrante</t>
+  </si>
+  <si>
+    <t>RESULTADO CORRECTO</t>
+  </si>
+  <si>
+    <t>SIN GESTIÓN AUTOMATIZACIÓN HDI</t>
+  </si>
+  <si>
+    <t>La diferencia es contabilizada por la Gerencia De Autoservicios y Efectivo de manera centralizada a la cuenta de sobrantes 279510020 el 18/03/2026</t>
+  </si>
+  <si>
+    <t>Cuadrado</t>
+  </si>
+  <si>
+    <t>El faltante $3.771.250 es cruzado con sobrante contabilizado el día 17/03/2026 ($3.771.250) el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>RESPUESTA CORRECTA</t>
+  </si>
+  <si>
+    <t>El faltante $3.771.250 es cruzado con sobrante contabilizado el día 17/03/2026 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>Faltante</t>
+  </si>
+  <si>
+    <t>La diferencia es contabilizada por la Gerencia De Autoservicios y Efectivo de manera centralizada a la cuenta de faltantes 168710093 el 18/03/2026, esta diferencia ingresa a proceso de investigación en el área para identificar a que corresponde.</t>
+  </si>
+  <si>
+    <r>
+      <t>El faltante $3.373.950 es cruzado con sobrante contabilizado el día 13/03/2026 ($1.180.000),</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> el día 12/03/2026 ($1.800.000)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, el día 11/03/2026 ($393.950) el cual es reversado por la seccion el día 18/03/2026</t>
+    </r>
+  </si>
+  <si>
+    <t>RESULTADO INCORRECTO</t>
+  </si>
+  <si>
+    <t>EL PENÚLTIMO ARQUEO QUE LA SUCURSAL REGISTRÓ FUE EL 06 DE MARZO, DESPUÉS DE ESTA FECHA SE GRABARON SOBRANTES POR CUADRE DIARIO EL 11, 12 Y 13 DE MARZO, LA AUTOMATIZACIÓN ESTÁ CRUZANDO LOS SOBRANTES DEL MÁS RECIENTE AL MÁS ANTIGUO Y DEBE SER DEL MÁS ANTIGUO DESPUÉS DEL PENÚLTIMO ARQUEO AL MÁS RECIENTE QUE SE GRABO POR CUADRE DIARIO; CON EL FIN DE CONTAR CON LOS SOBRANTES DISPONIBLES EN LAS FECHAS MÁS CERCANAS PARA LOS RECLAMOS DE LOS CLIENTES.</t>
+  </si>
+  <si>
+    <t>El faltante $3.373.950 es cruzado con sobrante contabilizado el día 11/03/2026 $399.900, sobrante contabilizado el día 12/03/2026 $1.800.000 y sobrante contabilizado el día 13/03/2026 $1.174.050  el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>EL CAJERO QUEDABA CUADRADO, LA AUTOMATIZACIÓN NO REALIZÓ EL CRUCE CON EL SOBRANTE</t>
+  </si>
+  <si>
+    <t>El faltante $490.000 es cruzado con sobrante contabilizado el día 04/03/2026 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $1.812.000 es cruzado con sobrante contabilizado el día 16/03/2026 ($1.520.000), el día 13/03/2026 ($292.000) el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>EL PENÚLTIMO ARQUEO QUE LA SUCURSAL REGISTRÓ FUE EL 11 DE MARZO, DESPUÉS DE ESTA FECHA SE GRABARON SOBRANTES POR CUADRE DIARIO EL 13 Y 16 DE MARZO, LA AUTOMATIZACIÓN ESTÁ CRUZANDO LOS SOBRANTES DEL MÁS RECIENTE AL MÁS ANTIGUO Y DEBE SER DEL MÁS ANTIGUO DESPUÉS DEL PENÚLTIMO ARQUEO AL MÁS RECIENTE QUE SE GRABO POR CUADRE DIARIO; CON EL FIN DE CONTAR CON LOS SOBRANTES DISPONIBLES EN LAS FECHAS MÁS CERCANAS PARA LOS RECLAMOS DE LOS CLIENTES.</t>
+  </si>
+  <si>
+    <t>El faltante $1.812.000 es cruzado con sobrante contabilizado el día 13/03/2026 $992.000 y sobrante contabilizado el día 16/03/2026 $820.000 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $590.000 es cruzado con sobrante contabilizado el día 05/03/2026 ($590.000) el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $590.000 es cruzado con sobrante contabilizado el día 05/03/2026 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $967.000 es cruzado con sobrante contabilizado el día 11/03/2026 ($967.000) el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $967.000 es cruzado con sobrante contabilizado el día 11/03/2026 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $3.691.000 es cruzado con sobrante contabilizado el día 11/03/2026 ($3.691.000) el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $3.691.000 es cruzado con sobrante contabilizado el día 11/03/2026 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $2.889.600 es cruzado con sobrante contabilizado el día 17/03/2026 ($2.235.000), el día 12/03/2026 ($654.600) el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>EL PENÚLTIMO ARQUEO QUE LA SUCURSAL REGISTRÓ FUE EL 05 DE MARZO, DESPUÉS DE ESTA FECHA SE GRABARON SOBRANTES POR CUADRE DIARIO EL 12 Y 17 DE MARZO, LA AUTOMATIZACIÓN ESTÁ CRUZANDO LOS SOBRANTES DEL MÁS RECIENTE AL MÁS ANTIGUO Y DEBE SER DEL MÁS ANTIGUO DESPUÉS DEL PENÚLTIMO ARQUEO AL MÁS RECIENTE QUE SE GRABO POR CUADRE DIARIO; CON EL FIN DE CONTAR CON LOS SOBRANTES DISPONIBLES EN LAS FECHAS MÁS CERCANAS PARA LOS RECLAMOS DE LOS CLIENTES.</t>
+  </si>
+  <si>
+    <t>El faltante $2.889.600 es cruzado con sobrante contabilizado el día 12/03/2026 $2.080.000 y sobrante contabilizado el día 17/03/2026 $809.600 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
+  <si>
+    <t>El faltante $1.390.000 es cruzado con sobrante contabilizado el día 4/03/2026 $310.000, sobrante contabilizado el día 06/03/2026 $880.000, sobrante contabilizado el día 10/03/2026 $190.000 y sobrante contabilizado el día 11/03/2026 $10.000 el cual es reversado por la seccion el día 18/03/2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3234,6 +3348,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3471,7 +3607,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3710,9 +3846,11 @@
     <xf numFmtId="43" fontId="0" fillId="20" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="21" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="23">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -3873,11 +4011,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Banca empresa"/>
       <sheetName val="Sucursales 2 dias"/>
@@ -19902,7 +20037,7 @@
 </file>
 
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <namedSheetView name="Vista 1" id="{65BC363A-CBC6-4A98-9BDE-F9918039A64C}"/>
   <namedSheetView name="Vista 2" id="{D2CE90FE-5E53-4A19-A8BD-0F6C734475D2}"/>
   <namedSheetView name="Vista 3" id="{3585CAA5-B1C5-48BF-AF31-671C813AD19F}"/>
@@ -19921,15 +20056,15 @@
 </file>
 
 <file path=xl/namedSheetViews/namedSheetView2.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <namedSheetView name="Vista 1" id="{67D4AD7F-679A-4660-8827-9908A5D17A9D}"/>
 </namedSheetViews>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -19967,7 +20102,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -20073,7 +20208,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -20215,7 +20350,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -20223,16 +20358,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA7671C-9926-4D00-BFA4-A7B2406C1955}">
-  <sheetPr codeName="Hoja3" filterMode="1"/>
-  <dimension ref="A1:AI521"/>
+  <sheetPr codeName="Hoja3"/>
+  <dimension ref="A1:AI552"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="6.90625" style="19" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.81640625" style="20" customWidth="1"/>
     <col min="8" max="8" width="14.81640625" customWidth="1"/>
     <col min="9" max="9" width="13.08984375" customWidth="1"/>
@@ -20295,7 +20430,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="70">
         <v>4</v>
       </c>
@@ -20349,7 +20484,7 @@
         <v>71278620</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="70">
         <v>4</v>
       </c>
@@ -20400,7 +20535,7 @@
         <v>71278620</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="70">
         <v>4</v>
       </c>
@@ -20451,7 +20586,7 @@
         <v>71278620</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="70">
         <v>5</v>
       </c>
@@ -20502,7 +20637,7 @@
         <v>43824478</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="70">
         <v>7</v>
       </c>
@@ -20553,7 +20688,7 @@
         <v>1017155472</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="70">
         <v>7</v>
       </c>
@@ -20606,7 +20741,7 @@
         <v>1017155472</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="70">
         <v>15</v>
       </c>
@@ -20657,7 +20792,7 @@
         <v>1037325417</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="70">
         <v>33</v>
       </c>
@@ -20708,7 +20843,7 @@
         <v>79659379</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="70">
         <v>54</v>
       </c>
@@ -20759,7 +20894,7 @@
         <v>1019068822</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="70">
         <v>60</v>
       </c>
@@ -20812,7 +20947,7 @@
         <v>14697128</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="70">
         <v>61</v>
       </c>
@@ -20863,7 +20998,7 @@
         <v>16497924</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="70">
         <v>77</v>
       </c>
@@ -20914,7 +21049,7 @@
         <v>94493031</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="70">
         <v>115</v>
       </c>
@@ -20965,7 +21100,7 @@
         <v>42158306</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="70">
         <v>185</v>
       </c>
@@ -21018,7 +21153,7 @@
         <v>66784636</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="71">
         <v>191</v>
       </c>
@@ -21069,7 +21204,7 @@
         <v>80812756</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="71">
         <v>221</v>
       </c>
@@ -21120,7 +21255,7 @@
         <v>52833254</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="70">
         <v>231</v>
       </c>
@@ -21171,7 +21306,7 @@
         <v>52979634</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="70">
         <v>236</v>
       </c>
@@ -21224,7 +21359,7 @@
         <v>71369714</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="70">
         <v>261</v>
       </c>
@@ -21275,7 +21410,7 @@
         <v>34327627</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="70">
         <v>262</v>
       </c>
@@ -21326,7 +21461,7 @@
         <v>1052378530</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="70">
         <v>264</v>
       </c>
@@ -21377,7 +21512,7 @@
         <v>1069722520</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="70">
         <v>291</v>
       </c>
@@ -21428,7 +21563,7 @@
         <v>1095930956</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="70">
         <v>291</v>
       </c>
@@ -21479,7 +21614,7 @@
         <v>1095930956</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="70">
         <v>318</v>
       </c>
@@ -21530,7 +21665,7 @@
         <v>1065862494</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="70">
         <v>318</v>
       </c>
@@ -21581,7 +21716,7 @@
         <v>1065862494</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="70">
         <v>322</v>
       </c>
@@ -21632,7 +21767,7 @@
         <v>1101320155</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="70">
         <v>332</v>
       </c>
@@ -21685,7 +21820,7 @@
         <v>80541675</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="70">
         <v>348</v>
       </c>
@@ -21738,7 +21873,7 @@
         <v>1123633014</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="70">
         <v>383</v>
       </c>
@@ -21789,7 +21924,7 @@
         <v>1073160492</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="72">
         <v>395</v>
       </c>
@@ -21840,7 +21975,7 @@
         <v>1121857901</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="70">
         <v>453</v>
       </c>
@@ -21891,7 +22026,7 @@
         <v>1083897578</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="70">
         <v>455</v>
       </c>
@@ -21942,7 +22077,7 @@
         <v>1083896352</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="70">
         <v>457</v>
       </c>
@@ -21993,7 +22128,7 @@
         <v>33750644</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="70">
         <v>523</v>
       </c>
@@ -22044,7 +22179,7 @@
         <v>1065609766</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="70">
         <v>554</v>
       </c>
@@ -22095,7 +22230,7 @@
         <v>1010130794</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="72">
         <v>554</v>
       </c>
@@ -22146,7 +22281,7 @@
         <v>1010130794</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="73">
         <v>556</v>
       </c>
@@ -22197,7 +22332,7 @@
         <v>39450196</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="70">
         <v>613</v>
       </c>
@@ -22248,7 +22383,7 @@
         <v>32106943</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="70">
         <v>634</v>
       </c>
@@ -22299,7 +22434,7 @@
         <v>1032424944</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="72">
         <v>651</v>
       </c>
@@ -22350,7 +22485,7 @@
         <v>70136398</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="70">
         <v>659</v>
       </c>
@@ -22401,7 +22536,7 @@
         <v>1110555222</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="70">
         <v>667</v>
       </c>
@@ -22452,7 +22587,7 @@
         <v>79953058</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="70">
         <v>682</v>
       </c>
@@ -22506,7 +22641,7 @@
         <v>1018447800</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="71">
         <v>698</v>
       </c>
@@ -22557,7 +22692,7 @@
         <v>1019065205</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="70">
         <v>723</v>
       </c>
@@ -22611,7 +22746,7 @@
         <v>1088310723</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="70">
         <v>725</v>
       </c>
@@ -22662,7 +22797,7 @@
         <v>1088032608</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="70">
         <v>728</v>
       </c>
@@ -22713,7 +22848,7 @@
         <v>1112783690</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="70">
         <v>728</v>
       </c>
@@ -22764,7 +22899,7 @@
         <v>1112783690</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="70">
         <v>781</v>
       </c>
@@ -22815,7 +22950,7 @@
         <v>1082848167</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="70">
         <v>796</v>
       </c>
@@ -22866,7 +23001,7 @@
         <v>1095802301</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="70">
         <v>849</v>
       </c>
@@ -22917,7 +23052,7 @@
         <v>86063461</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="70">
         <v>849</v>
       </c>
@@ -22968,7 +23103,7 @@
         <v>86063461</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="70">
         <v>852</v>
       </c>
@@ -23019,7 +23154,7 @@
         <v>1088251245</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="70">
         <v>866</v>
       </c>
@@ -23070,7 +23205,7 @@
         <v>1113674245</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="70">
         <v>876</v>
       </c>
@@ -23123,7 +23258,7 @@
         <v>1002032451</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="70">
         <v>888</v>
       </c>
@@ -23174,7 +23309,7 @@
         <v>1085921765</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="70">
         <v>907</v>
       </c>
@@ -23225,7 +23360,7 @@
         <v>71339401</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="70">
         <v>907</v>
       </c>
@@ -23276,7 +23411,7 @@
         <v>71339401</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="70">
         <v>946</v>
       </c>
@@ -23327,7 +23462,7 @@
         <v>20500181</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="70">
         <v>1</v>
       </c>
@@ -23378,7 +23513,7 @@
         <v>1017128064</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="70">
         <v>93</v>
       </c>
@@ -23429,7 +23564,7 @@
         <v>1067931735</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="70">
         <v>166</v>
       </c>
@@ -23480,7 +23615,7 @@
         <v>50938822</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="70">
         <v>185</v>
       </c>
@@ -23531,7 +23666,7 @@
         <v>66784636</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="70">
         <v>233</v>
       </c>
@@ -23582,7 +23717,7 @@
         <v>80271480</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="70">
         <v>291</v>
       </c>
@@ -23635,7 +23770,7 @@
         <v>1095930956</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="70">
         <v>331</v>
       </c>
@@ -23689,7 +23824,7 @@
         <v>32244978</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="70">
         <v>392</v>
       </c>
@@ -23742,7 +23877,7 @@
         <v>1054547012</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="70">
         <v>430</v>
       </c>
@@ -23793,7 +23928,7 @@
         <v>1035234232</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="70">
         <v>453</v>
       </c>
@@ -23844,7 +23979,7 @@
         <v>1083897578</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="70">
         <v>453</v>
       </c>
@@ -23895,7 +24030,7 @@
         <v>1083897578</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="70">
         <v>509</v>
       </c>
@@ -23946,7 +24081,7 @@
         <v>1143370364</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="70">
         <v>524</v>
       </c>
@@ -23997,7 +24132,7 @@
         <v>1004211532</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="70">
         <v>551</v>
       </c>
@@ -24048,7 +24183,7 @@
         <v>1152213498</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="72">
         <v>571</v>
       </c>
@@ -24099,7 +24234,7 @@
         <v>1019116828</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="70">
         <v>623</v>
       </c>
@@ -24150,7 +24285,7 @@
         <v>1060651791</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="72">
         <v>674</v>
       </c>
@@ -24204,7 +24339,7 @@
         <v>79813088</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="72">
         <v>678</v>
       </c>
@@ -24255,7 +24390,7 @@
         <v>1102586250</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="70">
         <v>692</v>
       </c>
@@ -24306,7 +24441,7 @@
         <v>30840635</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="70">
         <v>728</v>
       </c>
@@ -24360,7 +24495,7 @@
         <v>1112783690</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="70">
         <v>728</v>
       </c>
@@ -24413,7 +24548,7 @@
         <v>1112783690</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="70">
         <v>741</v>
       </c>
@@ -24464,7 +24599,7 @@
         <v>1130637714</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="70">
         <v>779</v>
       </c>
@@ -24517,7 +24652,7 @@
         <v>1082858126</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="72">
         <v>779</v>
       </c>
@@ -24568,7 +24703,7 @@
         <v>1082858126</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="70">
         <v>795</v>
       </c>
@@ -24619,7 +24754,7 @@
         <v>91274094</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="70">
         <v>849</v>
       </c>
@@ -24673,7 +24808,7 @@
         <v>86063461</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="70">
         <v>882</v>
       </c>
@@ -24724,7 +24859,7 @@
         <v>33369487</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="70">
         <v>927</v>
       </c>
@@ -24775,7 +24910,7 @@
         <v>1124849676</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="70">
         <v>937</v>
       </c>
@@ -24826,7 +24961,7 @@
         <v>1061702364</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="70">
         <v>941</v>
       </c>
@@ -24880,7 +25015,7 @@
         <v>1075228904</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="70">
         <v>946</v>
       </c>
@@ -24931,7 +25066,7 @@
         <v>20500181</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="72">
         <v>33</v>
       </c>
@@ -24982,7 +25117,7 @@
         <v>79659379</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="70">
         <v>61</v>
       </c>
@@ -25033,7 +25168,7 @@
         <v>1144070638</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="72">
         <v>70</v>
       </c>
@@ -25084,7 +25219,7 @@
         <v>30231139</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="72">
         <v>73</v>
       </c>
@@ -25137,7 +25272,7 @@
         <v>42157515</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="72">
         <v>74</v>
       </c>
@@ -25190,7 +25325,7 @@
         <v>59314706</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="72">
         <v>85</v>
       </c>
@@ -25241,7 +25376,7 @@
         <v>1047413788</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="72">
         <v>91</v>
       </c>
@@ -25292,7 +25427,7 @@
         <v>1067844638</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="70">
         <v>108</v>
       </c>
@@ -25343,7 +25478,7 @@
         <v>80206469</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="70">
         <v>167</v>
       </c>
@@ -25394,7 +25529,7 @@
         <v>80076538</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="72">
         <v>197</v>
       </c>
@@ -25445,7 +25580,7 @@
         <v>1065607404</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="70">
         <v>261</v>
       </c>
@@ -25496,7 +25631,7 @@
         <v>34327627</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="72">
         <v>279</v>
       </c>
@@ -25547,7 +25682,7 @@
         <v>42826913</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="72">
         <v>291</v>
       </c>
@@ -25598,7 +25733,7 @@
         <v>1095930956</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="70">
         <v>322</v>
       </c>
@@ -25649,7 +25784,7 @@
         <v>1101320155</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="72">
         <v>332</v>
       </c>
@@ -25700,7 +25835,7 @@
         <v>80541675</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="70">
         <v>395</v>
       </c>
@@ -25751,7 +25886,7 @@
         <v>1121857901</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="70">
         <v>395</v>
       </c>
@@ -25804,7 +25939,7 @@
         <v>1121857901</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="72">
         <v>451</v>
       </c>
@@ -25858,7 +25993,7 @@
         <v>1123206969</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="72">
         <v>453</v>
       </c>
@@ -25911,7 +26046,7 @@
         <v>1083897578</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="72">
         <v>499</v>
       </c>
@@ -25964,7 +26099,7 @@
         <v>71337474</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="72">
         <v>516</v>
       </c>
@@ -26015,7 +26150,7 @@
         <v>57292451</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="72">
         <v>523</v>
       </c>
@@ -26066,7 +26201,7 @@
         <v>39491642</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="72">
         <v>536</v>
       </c>
@@ -26119,7 +26254,7 @@
         <v>35891536</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="72">
         <v>609</v>
       </c>
@@ -26170,7 +26305,7 @@
         <v>98695047</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="72">
         <v>609</v>
       </c>
@@ -26221,7 +26356,7 @@
         <v>98695047</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="72">
         <v>623</v>
       </c>
@@ -26275,7 +26410,7 @@
         <v>1060651791</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="72">
         <v>667</v>
       </c>
@@ -26329,7 +26464,7 @@
         <v>79953058</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="72">
         <v>698</v>
       </c>
@@ -26380,7 +26515,7 @@
         <v>80177355</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="72">
         <v>750</v>
       </c>
@@ -26433,7 +26568,7 @@
         <v>31529631</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="72">
         <v>762</v>
       </c>
@@ -26484,7 +26619,7 @@
         <v>94364510</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="72">
         <v>781</v>
       </c>
@@ -26535,7 +26670,7 @@
         <v>1082848167</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="70">
         <v>795</v>
       </c>
@@ -26586,7 +26721,7 @@
         <v>91274094</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="72">
         <v>796</v>
       </c>
@@ -26637,7 +26772,7 @@
         <v>1095802301</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="72">
         <v>844</v>
       </c>
@@ -26688,7 +26823,7 @@
         <v>86058432</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="72">
         <v>849</v>
       </c>
@@ -26741,7 +26876,7 @@
         <v>86063461</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="72">
         <v>849</v>
       </c>
@@ -26795,7 +26930,7 @@
         <v>86063461</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="72">
         <v>866</v>
       </c>
@@ -26846,7 +26981,7 @@
         <v>1113674245</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="72">
         <v>890</v>
       </c>
@@ -26897,7 +27032,7 @@
         <v>1053835867</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="72">
         <v>915</v>
       </c>
@@ -26948,7 +27083,7 @@
         <v>52279779</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="72">
         <v>915</v>
       </c>
@@ -26999,7 +27134,7 @@
         <v>52279779</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="70">
         <v>916</v>
       </c>
@@ -27050,7 +27185,7 @@
         <v>1004306590</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="72">
         <v>331</v>
       </c>
@@ -27101,7 +27236,7 @@
         <v>32244978</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="72">
         <v>331</v>
       </c>
@@ -27152,7 +27287,7 @@
         <v>32244978</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="72">
         <v>395</v>
       </c>
@@ -27203,7 +27338,7 @@
         <v>1121857901</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="72">
         <v>185</v>
       </c>
@@ -27257,7 +27392,7 @@
         <v>66784636</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="72">
         <v>1</v>
       </c>
@@ -27308,7 +27443,7 @@
         <v>1017128064</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="72">
         <v>59</v>
       </c>
@@ -27359,7 +27494,7 @@
         <v>1060652821</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="72">
         <v>825</v>
       </c>
@@ -27410,7 +27545,7 @@
         <v>1144124243</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="72">
         <v>32</v>
       </c>
@@ -27461,7 +27596,7 @@
         <v>79750158</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="72">
         <v>275</v>
       </c>
@@ -27514,7 +27649,7 @@
         <v>16055613</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="72">
         <v>682</v>
       </c>
@@ -27567,7 +27702,7 @@
         <v>1018447800</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="72">
         <v>419</v>
       </c>
@@ -27620,7 +27755,7 @@
         <v>79248430</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="72">
         <v>8</v>
       </c>
@@ -27671,7 +27806,7 @@
         <v>71738191</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="72">
         <v>523</v>
       </c>
@@ -27722,7 +27857,7 @@
         <v>39491642</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="72">
         <v>265</v>
       </c>
@@ -27773,7 +27908,7 @@
         <v>1107081130</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="72">
         <v>634</v>
       </c>
@@ -27824,7 +27959,7 @@
         <v>1032424944</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="72">
         <v>430</v>
       </c>
@@ -27875,7 +28010,7 @@
         <v>1035234232</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="72">
         <v>743</v>
       </c>
@@ -27926,7 +28061,7 @@
         <v>79887183</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="72">
         <v>191</v>
       </c>
@@ -27977,7 +28112,7 @@
         <v>80812756</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="72">
         <v>937</v>
       </c>
@@ -28030,7 +28165,7 @@
         <v>1061702364</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="72">
         <v>292</v>
       </c>
@@ -28083,7 +28218,7 @@
         <v>44006127</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="72">
         <v>511</v>
       </c>
@@ -28134,7 +28269,7 @@
         <v>1037597003</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="72">
         <v>366</v>
       </c>
@@ -28185,7 +28320,7 @@
         <v>1035426009</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="72">
         <v>358</v>
       </c>
@@ -28236,7 +28371,7 @@
         <v>46456877</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="72">
         <v>388</v>
       </c>
@@ -28290,7 +28425,7 @@
         <v>1023890720</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="72">
         <v>253</v>
       </c>
@@ -28343,7 +28478,7 @@
         <v>1017241432</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="72">
         <v>432</v>
       </c>
@@ -28396,7 +28531,7 @@
         <v>71935844</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="72">
         <v>606</v>
       </c>
@@ -28449,7 +28584,7 @@
         <v>33368879</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="72">
         <v>16</v>
       </c>
@@ -28500,7 +28635,7 @@
         <v>1128391338</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="72">
         <v>941</v>
       </c>
@@ -28551,7 +28686,7 @@
         <v>1075228904</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="72">
         <v>54</v>
       </c>
@@ -28605,7 +28740,7 @@
         <v>1019068822</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="72">
         <v>178</v>
       </c>
@@ -28656,7 +28791,7 @@
         <v>79516051</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="72">
         <v>231</v>
       </c>
@@ -28709,7 +28844,7 @@
         <v>52979634</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="72">
         <v>79</v>
       </c>
@@ -28762,7 +28897,7 @@
         <v>79772242</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="72">
         <v>78</v>
       </c>
@@ -28815,7 +28950,7 @@
         <v>1098657131</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="72">
         <v>718</v>
       </c>
@@ -28868,7 +29003,7 @@
         <v>1110458168</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="72">
         <v>337</v>
       </c>
@@ -28919,7 +29054,7 @@
         <v>80386330</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="72">
         <v>317</v>
       </c>
@@ -28973,7 +29108,7 @@
         <v>1116796671</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="72">
         <v>352</v>
       </c>
@@ -29024,7 +29159,7 @@
         <v>28559006</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="72">
         <v>138</v>
       </c>
@@ -29078,7 +29213,7 @@
         <v>1023884092</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="72">
         <v>764</v>
       </c>
@@ -29129,7 +29264,7 @@
         <v>1112480917</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="72">
         <v>371</v>
       </c>
@@ -29182,7 +29317,7 @@
         <v>39279278</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="72">
         <v>888</v>
       </c>
@@ -29233,7 +29368,7 @@
         <v>1085921765</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="72">
         <v>741</v>
       </c>
@@ -29284,7 +29419,7 @@
         <v>1130637714</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="72">
         <v>651</v>
       </c>
@@ -29335,7 +29470,7 @@
         <v>70136398</v>
       </c>
     </row>
-    <row r="177" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A177" s="72">
         <v>41</v>
       </c>
@@ -29388,7 +29523,7 @@
         <v>94508187</v>
       </c>
     </row>
-    <row r="178" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A178" s="72">
         <v>623</v>
       </c>
@@ -29441,7 +29576,7 @@
         <v>1012348871</v>
       </c>
     </row>
-    <row r="179" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A179" s="72">
         <v>944</v>
       </c>
@@ -29495,7 +29630,7 @@
         <v>79644034</v>
       </c>
     </row>
-    <row r="180" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A180" s="72">
         <v>495</v>
       </c>
@@ -29546,7 +29681,7 @@
         <v>1052081923</v>
       </c>
     </row>
-    <row r="181" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A181" s="72">
         <v>728</v>
       </c>
@@ -29597,7 +29732,7 @@
         <v>1112783690</v>
       </c>
     </row>
-    <row r="182" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A182" s="72">
         <v>728</v>
       </c>
@@ -29648,7 +29783,7 @@
         <v>1112783690</v>
       </c>
     </row>
-    <row r="183" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A183" s="72">
         <v>78</v>
       </c>
@@ -29701,7 +29836,7 @@
         <v>1098657131</v>
       </c>
     </row>
-    <row r="184" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A184" s="72">
         <v>60</v>
       </c>
@@ -29752,7 +29887,7 @@
         <v>14697128</v>
       </c>
     </row>
-    <row r="185" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A185" s="72">
         <v>60</v>
       </c>
@@ -29803,7 +29938,7 @@
         <v>14697128</v>
       </c>
     </row>
-    <row r="186" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A186" s="72">
         <v>60</v>
       </c>
@@ -29856,7 +29991,7 @@
         <v>14697128</v>
       </c>
     </row>
-    <row r="187" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A187" s="72">
         <v>225</v>
       </c>
@@ -29909,7 +30044,7 @@
         <v>80212698</v>
       </c>
     </row>
-    <row r="188" spans="1:35" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A188" s="74">
         <v>442</v>
       </c>
@@ -29960,7 +30095,7 @@
         <v>1140853558</v>
       </c>
     </row>
-    <row r="189" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A189" s="72">
         <v>348</v>
       </c>
@@ -30033,7 +30168,7 @@
       <c r="AH189"/>
       <c r="AI189"/>
     </row>
-    <row r="190" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A190" s="72">
         <v>367</v>
       </c>
@@ -30103,7 +30238,7 @@
       <c r="AH190"/>
       <c r="AI190"/>
     </row>
-    <row r="191" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A191" s="72">
         <v>229</v>
       </c>
@@ -30173,7 +30308,7 @@
       <c r="AH191"/>
       <c r="AI191"/>
     </row>
-    <row r="192" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A192" s="72">
         <v>623</v>
       </c>
@@ -30243,7 +30378,7 @@
       <c r="AH192"/>
       <c r="AI192"/>
     </row>
-    <row r="193" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A193" s="72">
         <v>392</v>
       </c>
@@ -30313,7 +30448,7 @@
       <c r="AH193"/>
       <c r="AI193"/>
     </row>
-    <row r="194" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A194" s="72">
         <v>115</v>
       </c>
@@ -30383,7 +30518,7 @@
       <c r="AH194"/>
       <c r="AI194"/>
     </row>
-    <row r="195" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A195" s="72">
         <v>571</v>
       </c>
@@ -30453,7 +30588,7 @@
       <c r="AH195"/>
       <c r="AI195"/>
     </row>
-    <row r="196" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A196" s="72">
         <v>37</v>
       </c>
@@ -30523,7 +30658,7 @@
       <c r="AH196"/>
       <c r="AI196"/>
     </row>
-    <row r="197" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A197" s="72">
         <v>658</v>
       </c>
@@ -30593,7 +30728,7 @@
       <c r="AH197"/>
       <c r="AI197"/>
     </row>
-    <row r="198" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A198" s="72">
         <v>233</v>
       </c>
@@ -30663,7 +30798,7 @@
       <c r="AH198"/>
       <c r="AI198"/>
     </row>
-    <row r="199" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A199" s="72">
         <v>389</v>
       </c>
@@ -30733,7 +30868,7 @@
       <c r="AH199"/>
       <c r="AI199"/>
     </row>
-    <row r="200" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="72">
         <v>866</v>
       </c>
@@ -30803,7 +30938,7 @@
       <c r="AH200"/>
       <c r="AI200"/>
     </row>
-    <row r="201" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A201" s="72">
         <v>33</v>
       </c>
@@ -30873,7 +31008,7 @@
       <c r="AH201"/>
       <c r="AI201"/>
     </row>
-    <row r="202" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A202" s="72">
         <v>333</v>
       </c>
@@ -30943,7 +31078,7 @@
       <c r="AH202"/>
       <c r="AI202"/>
     </row>
-    <row r="203" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A203" s="72">
         <v>214</v>
       </c>
@@ -31015,7 +31150,7 @@
       <c r="AH203"/>
       <c r="AI203"/>
     </row>
-    <row r="204" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A204" s="72">
         <v>438</v>
       </c>
@@ -31088,7 +31223,7 @@
       <c r="AH204"/>
       <c r="AI204"/>
     </row>
-    <row r="205" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A205" s="72">
         <v>333</v>
       </c>
@@ -31160,7 +31295,7 @@
       <c r="AH205"/>
       <c r="AI205"/>
     </row>
-    <row r="206" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A206" s="72">
         <v>197</v>
       </c>
@@ -31230,7 +31365,7 @@
       <c r="AH206"/>
       <c r="AI206"/>
     </row>
-    <row r="207" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A207" s="72">
         <v>659</v>
       </c>
@@ -31300,7 +31435,7 @@
       <c r="AH207"/>
       <c r="AI207"/>
     </row>
-    <row r="208" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A208" s="72">
         <v>511</v>
       </c>
@@ -31370,7 +31505,7 @@
       <c r="AH208"/>
       <c r="AI208"/>
     </row>
-    <row r="209" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A209" s="72">
         <v>101</v>
       </c>
@@ -31440,7 +31575,7 @@
       <c r="AH209"/>
       <c r="AI209"/>
     </row>
-    <row r="210" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A210" s="72">
         <v>829</v>
       </c>
@@ -31510,7 +31645,7 @@
       <c r="AH210"/>
       <c r="AI210"/>
     </row>
-    <row r="211" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A211" s="72">
         <v>70</v>
       </c>
@@ -31582,7 +31717,7 @@
       <c r="AH211"/>
       <c r="AI211"/>
     </row>
-    <row r="212" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A212" s="72">
         <v>844</v>
       </c>
@@ -31654,7 +31789,7 @@
       <c r="AH212"/>
       <c r="AI212"/>
     </row>
-    <row r="213" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A213" s="72">
         <v>236</v>
       </c>
@@ -31692,13 +31827,13 @@
       <c r="L213" s="52" t="s">
         <v>746</v>
       </c>
-      <c r="M213" s="6">
+      <c r="M213" s="6" t="e">
         <f t="shared" si="14"/>
-        <v>-27520000</v>
-      </c>
-      <c r="N213" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N213" s="21" t="e">
         <f t="shared" si="15"/>
-        <v>Sobrante</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O213" s="9" t="s">
         <v>747</v>
@@ -31726,7 +31861,7 @@
       <c r="AH213"/>
       <c r="AI213"/>
     </row>
-    <row r="214" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A214" s="72">
         <v>96</v>
       </c>
@@ -31796,7 +31931,7 @@
       <c r="AH214"/>
       <c r="AI214"/>
     </row>
-    <row r="215" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A215" s="72">
         <v>172</v>
       </c>
@@ -31866,7 +32001,7 @@
       <c r="AH215"/>
       <c r="AI215"/>
     </row>
-    <row r="216" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A216" s="72">
         <v>166</v>
       </c>
@@ -31936,7 +32071,7 @@
       <c r="AH216"/>
       <c r="AI216"/>
     </row>
-    <row r="217" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="72">
         <v>291</v>
       </c>
@@ -32006,7 +32141,7 @@
       <c r="AH217"/>
       <c r="AI217"/>
     </row>
-    <row r="218" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A218" s="72">
         <v>915</v>
       </c>
@@ -32076,7 +32211,7 @@
       <c r="AH218"/>
       <c r="AI218"/>
     </row>
-    <row r="219" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A219" s="72">
         <v>915</v>
       </c>
@@ -32146,7 +32281,7 @@
       <c r="AH219"/>
       <c r="AI219"/>
     </row>
-    <row r="220" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A220" s="72">
         <v>556</v>
       </c>
@@ -32216,7 +32351,7 @@
       <c r="AH220"/>
       <c r="AI220"/>
     </row>
-    <row r="221" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A221" s="72">
         <v>728</v>
       </c>
@@ -32288,7 +32423,7 @@
       <c r="AH221"/>
       <c r="AI221"/>
     </row>
-    <row r="222" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A222" s="72">
         <v>728</v>
       </c>
@@ -32360,7 +32495,7 @@
       <c r="AH222"/>
       <c r="AI222"/>
     </row>
-    <row r="223" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A223" s="72">
         <v>541</v>
       </c>
@@ -32430,7 +32565,7 @@
       <c r="AH223"/>
       <c r="AI223"/>
     </row>
-    <row r="224" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A224" s="72">
         <v>85</v>
       </c>
@@ -32503,7 +32638,7 @@
       <c r="AH224"/>
       <c r="AI224"/>
     </row>
-    <row r="225" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A225" s="72">
         <v>849</v>
       </c>
@@ -32576,7 +32711,7 @@
       <c r="AH225"/>
       <c r="AI225"/>
     </row>
-    <row r="226" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A226" s="72">
         <v>499</v>
       </c>
@@ -32648,7 +32783,7 @@
       <c r="AH226"/>
       <c r="AI226"/>
     </row>
-    <row r="227" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A227" s="72">
         <v>916</v>
       </c>
@@ -32718,7 +32853,7 @@
       <c r="AH227"/>
       <c r="AI227"/>
     </row>
-    <row r="228" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A228" s="72">
         <v>300</v>
       </c>
@@ -32788,7 +32923,7 @@
       <c r="AH228"/>
       <c r="AI228"/>
     </row>
-    <row r="229" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A229" s="72">
         <v>667</v>
       </c>
@@ -32858,7 +32993,7 @@
       <c r="AH229"/>
       <c r="AI229"/>
     </row>
-    <row r="230" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A230" s="72">
         <v>541</v>
       </c>
@@ -32928,7 +33063,7 @@
       <c r="AH230"/>
       <c r="AI230"/>
     </row>
-    <row r="231" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A231" s="72">
         <v>674</v>
       </c>
@@ -33001,7 +33136,7 @@
       <c r="AH231"/>
       <c r="AI231"/>
     </row>
-    <row r="232" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="72">
         <v>395</v>
       </c>
@@ -33071,7 +33206,7 @@
       <c r="AH232"/>
       <c r="AI232"/>
     </row>
-    <row r="233" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="72">
         <v>395</v>
       </c>
@@ -33141,7 +33276,7 @@
       <c r="AH233"/>
       <c r="AI233"/>
     </row>
-    <row r="234" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="72">
         <v>867</v>
       </c>
@@ -33211,7 +33346,7 @@
       <c r="AH234"/>
       <c r="AI234"/>
     </row>
-    <row r="235" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A235" s="72">
         <v>517</v>
       </c>
@@ -33281,7 +33416,7 @@
       <c r="AH235"/>
       <c r="AI235"/>
     </row>
-    <row r="236" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A236" s="72">
         <v>781</v>
       </c>
@@ -33351,7 +33486,7 @@
       <c r="AH236"/>
       <c r="AI236"/>
     </row>
-    <row r="237" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="72">
         <v>115</v>
       </c>
@@ -33421,7 +33556,7 @@
       <c r="AH237"/>
       <c r="AI237"/>
     </row>
-    <row r="238" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" s="72">
         <v>523</v>
       </c>
@@ -33491,7 +33626,7 @@
       <c r="AH238"/>
       <c r="AI238"/>
     </row>
-    <row r="239" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="72">
         <v>291</v>
       </c>
@@ -33563,7 +33698,7 @@
       <c r="AH239"/>
       <c r="AI239"/>
     </row>
-    <row r="240" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A240" s="72">
         <v>76</v>
       </c>
@@ -33636,7 +33771,7 @@
       <c r="AH240"/>
       <c r="AI240"/>
     </row>
-    <row r="241" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A241" s="72">
         <v>725</v>
       </c>
@@ -33708,7 +33843,7 @@
       <c r="AH241"/>
       <c r="AI241"/>
     </row>
-    <row r="242" spans="1:35" s="36" customFormat="1" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:35" s="36" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="72">
         <v>667</v>
       </c>
@@ -33778,7 +33913,7 @@
       <c r="AH242"/>
       <c r="AI242"/>
     </row>
-    <row r="243" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="72">
         <v>756</v>
       </c>
@@ -33850,7 +33985,7 @@
       <c r="AH243"/>
       <c r="AI243"/>
     </row>
-    <row r="244" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="72">
         <v>698</v>
       </c>
@@ -33920,7 +34055,7 @@
       <c r="AH244"/>
       <c r="AI244"/>
     </row>
-    <row r="245" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A245" s="72">
         <v>383</v>
       </c>
@@ -33992,7 +34127,7 @@
       <c r="AH245"/>
       <c r="AI245"/>
     </row>
-    <row r="246" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A246" s="72">
         <v>455</v>
       </c>
@@ -34064,7 +34199,7 @@
       <c r="AH246"/>
       <c r="AI246"/>
     </row>
-    <row r="247" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A247" s="72">
         <v>844</v>
       </c>
@@ -34137,7 +34272,7 @@
       <c r="AH247"/>
       <c r="AI247"/>
     </row>
-    <row r="248" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="72">
         <v>820</v>
       </c>
@@ -34210,7 +34345,7 @@
       <c r="AH248"/>
       <c r="AI248"/>
     </row>
-    <row r="249" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="72">
         <v>477</v>
       </c>
@@ -34282,7 +34417,7 @@
       <c r="AH249"/>
       <c r="AI249"/>
     </row>
-    <row r="250" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="72">
         <v>613</v>
       </c>
@@ -34352,7 +34487,7 @@
       <c r="AH250"/>
       <c r="AI250"/>
     </row>
-    <row r="251" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="72">
         <v>385</v>
       </c>
@@ -34422,7 +34557,7 @@
       <c r="AH251"/>
       <c r="AI251"/>
     </row>
-    <row r="252" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="72">
         <v>848</v>
       </c>
@@ -34494,7 +34629,7 @@
       <c r="AH252"/>
       <c r="AI252"/>
     </row>
-    <row r="253" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="72">
         <v>569</v>
       </c>
@@ -34564,7 +34699,7 @@
       <c r="AH253"/>
       <c r="AI253"/>
     </row>
-    <row r="254" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="72">
         <v>291</v>
       </c>
@@ -34637,7 +34772,7 @@
       <c r="AH254"/>
       <c r="AI254"/>
     </row>
-    <row r="255" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="72">
         <v>556</v>
       </c>
@@ -34709,7 +34844,7 @@
       <c r="AH255"/>
       <c r="AI255"/>
     </row>
-    <row r="256" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="72">
         <v>495</v>
       </c>
@@ -34779,7 +34914,7 @@
       <c r="AH256"/>
       <c r="AI256"/>
     </row>
-    <row r="257" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="72">
         <v>60</v>
       </c>
@@ -34849,7 +34984,7 @@
       <c r="AH257"/>
       <c r="AI257"/>
     </row>
-    <row r="258" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="72">
         <v>60</v>
       </c>
@@ -34921,7 +35056,7 @@
       <c r="AH258"/>
       <c r="AI258"/>
     </row>
-    <row r="259" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="72">
         <v>451</v>
       </c>
@@ -34994,7 +35129,7 @@
       <c r="AH259"/>
       <c r="AI259"/>
     </row>
-    <row r="260" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="72">
         <v>367</v>
       </c>
@@ -35066,7 +35201,7 @@
       <c r="AH260"/>
       <c r="AI260"/>
     </row>
-    <row r="261" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="72">
         <v>890</v>
       </c>
@@ -35138,7 +35273,7 @@
       <c r="AH261"/>
       <c r="AI261"/>
     </row>
-    <row r="262" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A262" s="72">
         <v>516</v>
       </c>
@@ -35208,7 +35343,7 @@
       <c r="AH262"/>
       <c r="AI262"/>
     </row>
-    <row r="263" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A263" s="72">
         <v>265</v>
       </c>
@@ -35278,7 +35413,7 @@
       <c r="AH263"/>
       <c r="AI263"/>
     </row>
-    <row r="264" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A264" s="72">
         <v>725</v>
       </c>
@@ -35348,7 +35483,7 @@
       <c r="AH264"/>
       <c r="AI264"/>
     </row>
-    <row r="265" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A265" s="72">
         <v>728</v>
       </c>
@@ -35418,7 +35553,7 @@
       <c r="AH265"/>
       <c r="AI265"/>
     </row>
-    <row r="266" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A266" s="72">
         <v>728</v>
       </c>
@@ -35488,7 +35623,7 @@
       <c r="AH266"/>
       <c r="AI266"/>
     </row>
-    <row r="267" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="72">
         <v>333</v>
       </c>
@@ -35558,7 +35693,7 @@
       <c r="AH267"/>
       <c r="AI267"/>
     </row>
-    <row r="268" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="72">
         <v>214</v>
       </c>
@@ -35631,7 +35766,7 @@
       <c r="AH268"/>
       <c r="AI268"/>
     </row>
-    <row r="269" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="72">
         <v>692</v>
       </c>
@@ -35701,7 +35836,7 @@
       <c r="AH269"/>
       <c r="AI269"/>
     </row>
-    <row r="270" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="72">
         <v>692</v>
       </c>
@@ -35771,7 +35906,7 @@
       <c r="AH270"/>
       <c r="AI270"/>
     </row>
-    <row r="271" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="72">
         <v>395</v>
       </c>
@@ -35844,7 +35979,7 @@
       <c r="AH271"/>
       <c r="AI271"/>
     </row>
-    <row r="272" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="72">
         <v>395</v>
       </c>
@@ -35916,7 +36051,7 @@
       <c r="AH272"/>
       <c r="AI272"/>
     </row>
-    <row r="273" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="72">
         <v>167</v>
       </c>
@@ -35986,7 +36121,7 @@
       <c r="AH273"/>
       <c r="AI273"/>
     </row>
-    <row r="274" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A274" s="72">
         <v>81</v>
       </c>
@@ -36058,7 +36193,7 @@
       <c r="AH274"/>
       <c r="AI274"/>
     </row>
-    <row r="275" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A275" s="72">
         <v>154</v>
       </c>
@@ -36130,7 +36265,7 @@
       <c r="AH275"/>
       <c r="AI275"/>
     </row>
-    <row r="276" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A276" s="72">
         <v>852</v>
       </c>
@@ -36202,7 +36337,7 @@
       <c r="AH276"/>
       <c r="AI276"/>
     </row>
-    <row r="277" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A277" s="72">
         <v>7</v>
       </c>
@@ -36275,7 +36410,7 @@
       <c r="AH277"/>
       <c r="AI277"/>
     </row>
-    <row r="278" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A278" s="72">
         <v>333</v>
       </c>
@@ -36348,7 +36483,7 @@
       <c r="AH278"/>
       <c r="AI278"/>
     </row>
-    <row r="279" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="72">
         <v>419</v>
       </c>
@@ -36418,7 +36553,7 @@
       <c r="AH279"/>
       <c r="AI279"/>
     </row>
-    <row r="280" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A280" s="72">
         <v>523</v>
       </c>
@@ -36490,7 +36625,7 @@
       <c r="AH280"/>
       <c r="AI280"/>
     </row>
-    <row r="281" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A281" s="72">
         <v>659</v>
       </c>
@@ -36560,7 +36695,7 @@
       <c r="AH281"/>
       <c r="AI281"/>
     </row>
-    <row r="282" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A282" s="72">
         <v>191</v>
       </c>
@@ -36630,7 +36765,7 @@
       <c r="AH282"/>
       <c r="AI282"/>
     </row>
-    <row r="283" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A283" s="72">
         <v>789</v>
       </c>
@@ -36668,13 +36803,13 @@
       <c r="L283" s="52" t="s">
         <v>804</v>
       </c>
-      <c r="M283" s="6">
+      <c r="M283" s="6" t="e">
         <f t="shared" si="22"/>
-        <v>-2270000</v>
-      </c>
-      <c r="N283" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N283" s="21" t="e">
         <f t="shared" si="23"/>
-        <v>Sobrante</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O283" s="9" t="s">
         <v>806</v>
@@ -36702,7 +36837,7 @@
       <c r="AH283"/>
       <c r="AI283"/>
     </row>
-    <row r="284" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A284" s="72">
         <v>40</v>
       </c>
@@ -36772,7 +36907,7 @@
       <c r="AH284"/>
       <c r="AI284"/>
     </row>
-    <row r="285" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A285" s="72">
         <v>812</v>
       </c>
@@ -36842,7 +36977,7 @@
       <c r="AH285"/>
       <c r="AI285"/>
     </row>
-    <row r="286" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A286" s="72">
         <v>358</v>
       </c>
@@ -36912,7 +37047,7 @@
       <c r="AH286"/>
       <c r="AI286"/>
     </row>
-    <row r="287" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A287" s="72">
         <v>70</v>
       </c>
@@ -36982,7 +37117,7 @@
       <c r="AH287"/>
       <c r="AI287"/>
     </row>
-    <row r="288" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A288" s="72">
         <v>363</v>
       </c>
@@ -37052,7 +37187,7 @@
       <c r="AH288"/>
       <c r="AI288"/>
     </row>
-    <row r="289" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A289" s="72">
         <v>302</v>
       </c>
@@ -37124,7 +37259,7 @@
       <c r="AH289"/>
       <c r="AI289"/>
     </row>
-    <row r="290" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A290" s="72">
         <v>253</v>
       </c>
@@ -37194,7 +37329,7 @@
       <c r="AH290"/>
       <c r="AI290"/>
     </row>
-    <row r="291" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A291" s="72">
         <v>716</v>
       </c>
@@ -37264,7 +37399,7 @@
       <c r="AH291"/>
       <c r="AI291"/>
     </row>
-    <row r="292" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A292" s="72">
         <v>674</v>
       </c>
@@ -37337,7 +37472,7 @@
       <c r="AH292"/>
       <c r="AI292"/>
     </row>
-    <row r="293" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A293" s="72">
         <v>606</v>
       </c>
@@ -37407,7 +37542,7 @@
       <c r="AH293"/>
       <c r="AI293"/>
     </row>
-    <row r="294" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A294" s="72">
         <v>625</v>
       </c>
@@ -37479,7 +37614,7 @@
       <c r="AH294"/>
       <c r="AI294"/>
     </row>
-    <row r="295" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A295" s="72">
         <v>352</v>
       </c>
@@ -37549,7 +37684,7 @@
       <c r="AH295"/>
       <c r="AI295"/>
     </row>
-    <row r="296" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A296" s="72">
         <v>843</v>
       </c>
@@ -37619,7 +37754,7 @@
       <c r="AH296"/>
       <c r="AI296"/>
     </row>
-    <row r="297" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A297" s="72">
         <v>371</v>
       </c>
@@ -37689,7 +37824,7 @@
       <c r="AH297"/>
       <c r="AI297"/>
     </row>
-    <row r="298" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A298" s="72">
         <v>506</v>
       </c>
@@ -37759,7 +37894,7 @@
       <c r="AH298"/>
       <c r="AI298"/>
     </row>
-    <row r="299" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A299" s="72">
         <v>812</v>
       </c>
@@ -37831,7 +37966,7 @@
       <c r="AH299"/>
       <c r="AI299"/>
     </row>
-    <row r="300" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A300" s="72">
         <v>812</v>
       </c>
@@ -37903,7 +38038,7 @@
       <c r="AH300"/>
       <c r="AI300"/>
     </row>
-    <row r="301" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A301" s="72">
         <v>476</v>
       </c>
@@ -37973,7 +38108,7 @@
       <c r="AH301"/>
       <c r="AI301"/>
     </row>
-    <row r="302" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A302" s="72">
         <v>7</v>
       </c>
@@ -38043,7 +38178,7 @@
       <c r="AH302"/>
       <c r="AI302"/>
     </row>
-    <row r="303" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A303" s="72">
         <v>609</v>
       </c>
@@ -38113,7 +38248,7 @@
       <c r="AH303"/>
       <c r="AI303"/>
     </row>
-    <row r="304" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A304" s="72">
         <v>609</v>
       </c>
@@ -38183,7 +38318,7 @@
       <c r="AH304"/>
       <c r="AI304"/>
     </row>
-    <row r="305" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A305" s="72">
         <v>166</v>
       </c>
@@ -38253,7 +38388,7 @@
       <c r="AH305"/>
       <c r="AI305"/>
     </row>
-    <row r="306" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A306" s="72">
         <v>166</v>
       </c>
@@ -38325,7 +38460,7 @@
       <c r="AH306"/>
       <c r="AI306"/>
     </row>
-    <row r="307" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A307" s="72">
         <v>419</v>
       </c>
@@ -38395,7 +38530,7 @@
       <c r="AH307"/>
       <c r="AI307"/>
     </row>
-    <row r="308" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A308" s="72">
         <v>810</v>
       </c>
@@ -38467,7 +38602,7 @@
       <c r="AH308"/>
       <c r="AI308"/>
     </row>
-    <row r="309" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A309" s="72">
         <v>915</v>
       </c>
@@ -38537,7 +38672,7 @@
       <c r="AH309"/>
       <c r="AI309"/>
     </row>
-    <row r="310" spans="1:35" s="36" customFormat="1" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:35" s="36" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="72">
         <v>495</v>
       </c>
@@ -38609,7 +38744,7 @@
       <c r="AH310"/>
       <c r="AI310"/>
     </row>
-    <row r="311" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A311" s="72">
         <v>193</v>
       </c>
@@ -38679,7 +38814,7 @@
       <c r="AH311"/>
       <c r="AI311"/>
     </row>
-    <row r="312" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A312" s="72">
         <v>33</v>
       </c>
@@ -38749,7 +38884,7 @@
       <c r="AH312"/>
       <c r="AI312"/>
     </row>
-    <row r="313" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A313" s="72">
         <v>225</v>
       </c>
@@ -38787,13 +38922,13 @@
       <c r="L313" s="52" t="s">
         <v>803</v>
       </c>
-      <c r="M313" s="6">
+      <c r="M313" s="6" t="e">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="N313" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N313" s="21" t="e">
         <f t="shared" si="23"/>
-        <v>Cuadrado</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O313" s="4" t="s">
         <v>590</v>
@@ -38821,7 +38956,7 @@
       <c r="AH313"/>
       <c r="AI313"/>
     </row>
-    <row r="314" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A314" s="72">
         <v>721</v>
       </c>
@@ -38891,7 +39026,7 @@
       <c r="AH314"/>
       <c r="AI314"/>
     </row>
-    <row r="315" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A315" s="72">
         <v>721</v>
       </c>
@@ -38961,7 +39096,7 @@
       <c r="AH315"/>
       <c r="AI315"/>
     </row>
-    <row r="316" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A316" s="72">
         <v>890</v>
       </c>
@@ -39033,7 +39168,7 @@
       <c r="AH316"/>
       <c r="AI316"/>
     </row>
-    <row r="317" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A317" s="72">
         <v>229</v>
       </c>
@@ -39105,7 +39240,7 @@
       <c r="AH317"/>
       <c r="AI317"/>
     </row>
-    <row r="318" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A318" s="72">
         <v>229</v>
       </c>
@@ -39175,7 +39310,7 @@
       <c r="AH318"/>
       <c r="AI318"/>
     </row>
-    <row r="319" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A319" s="72">
         <v>849</v>
       </c>
@@ -39247,7 +39382,7 @@
       <c r="AH319"/>
       <c r="AI319"/>
     </row>
-    <row r="320" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A320" s="72">
         <v>849</v>
       </c>
@@ -39319,7 +39454,7 @@
       <c r="AH320"/>
       <c r="AI320"/>
     </row>
-    <row r="321" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A321" s="72">
         <v>499</v>
       </c>
@@ -39389,7 +39524,7 @@
       <c r="AH321"/>
       <c r="AI321"/>
     </row>
-    <row r="322" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A322" s="72">
         <v>264</v>
       </c>
@@ -39459,7 +39594,7 @@
       <c r="AH322"/>
       <c r="AI322"/>
     </row>
-    <row r="323" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A323" s="72">
         <v>61</v>
       </c>
@@ -39529,7 +39664,7 @@
       <c r="AH323"/>
       <c r="AI323"/>
     </row>
-    <row r="324" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A324" s="72">
         <v>277</v>
       </c>
@@ -39602,7 +39737,7 @@
       <c r="AH324"/>
       <c r="AI324"/>
     </row>
-    <row r="325" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A325" s="72">
         <v>511</v>
       </c>
@@ -39672,7 +39807,7 @@
       <c r="AH325"/>
       <c r="AI325"/>
     </row>
-    <row r="326" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A326" s="72">
         <v>300</v>
       </c>
@@ -39742,7 +39877,7 @@
       <c r="AH326"/>
       <c r="AI326"/>
     </row>
-    <row r="327" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A327" s="72">
         <v>888</v>
       </c>
@@ -39812,7 +39947,7 @@
       <c r="AH327"/>
       <c r="AI327"/>
     </row>
-    <row r="328" spans="1:35" s="36" customFormat="1" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:35" s="36" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="72">
         <v>651</v>
       </c>
@@ -39956,7 +40091,7 @@
       <c r="AH329"/>
       <c r="AI329"/>
     </row>
-    <row r="330" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A330" s="72">
         <v>481</v>
       </c>
@@ -40026,7 +40161,7 @@
       <c r="AH330"/>
       <c r="AI330"/>
     </row>
-    <row r="331" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A331" s="72">
         <v>795</v>
       </c>
@@ -40096,7 +40231,7 @@
       <c r="AH331"/>
       <c r="AI331"/>
     </row>
-    <row r="332" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A332" s="72">
         <v>795</v>
       </c>
@@ -40166,7 +40301,7 @@
       <c r="AH332"/>
       <c r="AI332"/>
     </row>
-    <row r="333" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A333" s="72">
         <v>745</v>
       </c>
@@ -40236,7 +40371,7 @@
       <c r="AH333"/>
       <c r="AI333"/>
     </row>
-    <row r="334" spans="1:35" s="36" customFormat="1" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:35" s="36" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="72">
         <v>777</v>
       </c>
@@ -40308,7 +40443,7 @@
       <c r="AH334"/>
       <c r="AI334"/>
     </row>
-    <row r="335" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A335" s="72">
         <v>6</v>
       </c>
@@ -40380,7 +40515,7 @@
       <c r="AH335"/>
       <c r="AI335"/>
     </row>
-    <row r="336" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A336" s="72">
         <v>361</v>
       </c>
@@ -40450,7 +40585,7 @@
       <c r="AH336"/>
       <c r="AI336"/>
     </row>
-    <row r="337" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A337" s="72">
         <v>777</v>
       </c>
@@ -40522,7 +40657,7 @@
       <c r="AH337"/>
       <c r="AI337"/>
     </row>
-    <row r="338" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A338" s="72">
         <v>277</v>
       </c>
@@ -40594,7 +40729,7 @@
       <c r="AH338"/>
       <c r="AI338"/>
     </row>
-    <row r="339" spans="1:35" s="36" customFormat="1" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:35" s="36" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="72">
         <v>723</v>
       </c>
@@ -40667,7 +40802,7 @@
       <c r="AH339"/>
       <c r="AI339"/>
     </row>
-    <row r="340" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A340" s="72">
         <v>769</v>
       </c>
@@ -40739,7 +40874,7 @@
       <c r="AH340"/>
       <c r="AI340"/>
     </row>
-    <row r="341" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A341" s="72">
         <v>19</v>
       </c>
@@ -40809,7 +40944,7 @@
       <c r="AH341"/>
       <c r="AI341"/>
     </row>
-    <row r="342" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A342" s="72">
         <v>291</v>
       </c>
@@ -40879,7 +41014,7 @@
       <c r="AH342"/>
       <c r="AI342"/>
     </row>
-    <row r="343" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A343" s="72">
         <v>91</v>
       </c>
@@ -40949,7 +41084,7 @@
       <c r="AH343"/>
       <c r="AI343"/>
     </row>
-    <row r="344" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A344" s="72">
         <v>806</v>
       </c>
@@ -41019,7 +41154,7 @@
       <c r="AH344"/>
       <c r="AI344"/>
     </row>
-    <row r="345" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A345" s="72">
         <v>750</v>
       </c>
@@ -41091,7 +41226,7 @@
       <c r="AH345"/>
       <c r="AI345"/>
     </row>
-    <row r="346" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A346" s="72">
         <v>253</v>
       </c>
@@ -41163,7 +41298,7 @@
       <c r="AH346"/>
       <c r="AI346"/>
     </row>
-    <row r="347" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A347" s="72">
         <v>198</v>
       </c>
@@ -41235,7 +41370,7 @@
       <c r="AH347"/>
       <c r="AI347"/>
     </row>
-    <row r="348" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A348" s="72">
         <v>664</v>
       </c>
@@ -41308,7 +41443,7 @@
       <c r="AH348"/>
       <c r="AI348"/>
     </row>
-    <row r="349" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A349" s="72">
         <v>77</v>
       </c>
@@ -41378,7 +41513,7 @@
       <c r="AH349"/>
       <c r="AI349"/>
     </row>
-    <row r="350" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A350" s="72">
         <v>793</v>
       </c>
@@ -41448,7 +41583,7 @@
       <c r="AH350"/>
       <c r="AI350"/>
     </row>
-    <row r="351" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A351" s="72">
         <v>16</v>
       </c>
@@ -41520,7 +41655,7 @@
       <c r="AH351"/>
       <c r="AI351"/>
     </row>
-    <row r="352" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A352" s="72">
         <v>221</v>
       </c>
@@ -41590,7 +41725,7 @@
       <c r="AH352"/>
       <c r="AI352"/>
     </row>
-    <row r="353" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A353" s="72">
         <v>946</v>
       </c>
@@ -41660,7 +41795,7 @@
       <c r="AH353"/>
       <c r="AI353"/>
     </row>
-    <row r="354" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A354" s="72">
         <v>678</v>
       </c>
@@ -41732,7 +41867,7 @@
       <c r="AH354"/>
       <c r="AI354"/>
     </row>
-    <row r="355" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A355" s="72">
         <v>820</v>
       </c>
@@ -41805,7 +41940,7 @@
       <c r="AH355"/>
       <c r="AI355"/>
     </row>
-    <row r="356" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A356" s="72">
         <v>477</v>
       </c>
@@ -41877,7 +42012,7 @@
       <c r="AH356"/>
       <c r="AI356"/>
     </row>
-    <row r="357" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A357" s="72">
         <v>337</v>
       </c>
@@ -41947,7 +42082,7 @@
       <c r="AH357"/>
       <c r="AI357"/>
     </row>
-    <row r="358" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A358" s="72">
         <v>379</v>
       </c>
@@ -42019,7 +42154,7 @@
       <c r="AH358"/>
       <c r="AI358"/>
     </row>
-    <row r="359" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A359" s="72">
         <v>352</v>
       </c>
@@ -42089,7 +42224,7 @@
       <c r="AH359"/>
       <c r="AI359"/>
     </row>
-    <row r="360" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A360" s="72">
         <v>96</v>
       </c>
@@ -42159,7 +42294,7 @@
       <c r="AH360"/>
       <c r="AI360"/>
     </row>
-    <row r="361" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A361" s="72">
         <v>677</v>
       </c>
@@ -42231,7 +42366,7 @@
       <c r="AH361"/>
       <c r="AI361"/>
     </row>
-    <row r="362" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A362" s="72">
         <v>484</v>
       </c>
@@ -42301,7 +42436,7 @@
       <c r="AH362"/>
       <c r="AI362"/>
     </row>
-    <row r="363" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A363" s="72">
         <v>41</v>
       </c>
@@ -42339,13 +42474,13 @@
       <c r="L363" s="52" t="s">
         <v>835</v>
       </c>
-      <c r="M363" s="6">
+      <c r="M363" s="6" t="e">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="N363" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N363" s="21" t="e">
         <f t="shared" si="27"/>
-        <v>Cuadrado</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O363" s="4" t="s">
         <v>590</v>
@@ -42373,7 +42508,7 @@
       <c r="AH363"/>
       <c r="AI363"/>
     </row>
-    <row r="364" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A364" s="72">
         <v>172</v>
       </c>
@@ -42443,7 +42578,7 @@
       <c r="AH364"/>
       <c r="AI364"/>
     </row>
-    <row r="365" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A365" s="72">
         <v>318</v>
       </c>
@@ -42515,7 +42650,7 @@
       <c r="AH365"/>
       <c r="AI365"/>
     </row>
-    <row r="366" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A366" s="72">
         <v>91</v>
       </c>
@@ -42587,7 +42722,7 @@
       <c r="AH366"/>
       <c r="AI366"/>
     </row>
-    <row r="367" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A367" s="72">
         <v>693</v>
       </c>
@@ -42657,7 +42792,7 @@
       <c r="AH367"/>
       <c r="AI367"/>
     </row>
-    <row r="368" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A368" s="72">
         <v>569</v>
       </c>
@@ -42727,7 +42862,7 @@
       <c r="AH368"/>
       <c r="AI368"/>
     </row>
-    <row r="369" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A369" s="72">
         <v>291</v>
       </c>
@@ -42797,7 +42932,7 @@
       <c r="AH369"/>
       <c r="AI369"/>
     </row>
-    <row r="370" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A370" s="72">
         <v>769</v>
       </c>
@@ -42867,7 +43002,7 @@
       <c r="AH370"/>
       <c r="AI370"/>
     </row>
-    <row r="371" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A371" s="72">
         <v>85</v>
       </c>
@@ -42939,7 +43074,7 @@
       <c r="AH371"/>
       <c r="AI371"/>
     </row>
-    <row r="372" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A372" s="72">
         <v>957</v>
       </c>
@@ -43009,7 +43144,7 @@
       <c r="AH372"/>
       <c r="AI372"/>
     </row>
-    <row r="373" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A373" s="72">
         <v>957</v>
       </c>
@@ -43079,7 +43214,7 @@
       <c r="AH373"/>
       <c r="AI373"/>
     </row>
-    <row r="374" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A374" s="72">
         <v>516</v>
       </c>
@@ -43151,7 +43286,7 @@
       <c r="AH374"/>
       <c r="AI374"/>
     </row>
-    <row r="375" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A375" s="72">
         <v>481</v>
       </c>
@@ -43221,7 +43356,7 @@
       <c r="AH375"/>
       <c r="AI375"/>
     </row>
-    <row r="376" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A376" s="72">
         <v>795</v>
       </c>
@@ -43291,7 +43426,7 @@
       <c r="AH376"/>
       <c r="AI376"/>
     </row>
-    <row r="377" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A377" s="72">
         <v>32</v>
       </c>
@@ -43361,7 +43496,7 @@
       <c r="AH377"/>
       <c r="AI377"/>
     </row>
-    <row r="378" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A378" s="72">
         <v>517</v>
       </c>
@@ -43431,7 +43566,7 @@
       <c r="AH378"/>
       <c r="AI378"/>
     </row>
-    <row r="379" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A379" s="72">
         <v>115</v>
       </c>
@@ -43501,7 +43636,7 @@
       <c r="AH379"/>
       <c r="AI379"/>
     </row>
-    <row r="380" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A380" s="72">
         <v>318</v>
       </c>
@@ -43571,7 +43706,7 @@
       <c r="AH380"/>
       <c r="AI380"/>
     </row>
-    <row r="381" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A381" s="72">
         <v>725</v>
       </c>
@@ -43644,7 +43779,7 @@
       <c r="AH381"/>
       <c r="AI381"/>
     </row>
-    <row r="382" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A382" s="72">
         <v>302</v>
       </c>
@@ -43716,7 +43851,7 @@
       <c r="AH382"/>
       <c r="AI382"/>
     </row>
-    <row r="383" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A383" s="72">
         <v>93</v>
       </c>
@@ -43786,7 +43921,7 @@
       <c r="AH383"/>
       <c r="AI383"/>
     </row>
-    <row r="384" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A384" s="72">
         <v>725</v>
       </c>
@@ -43856,7 +43991,7 @@
       <c r="AH384"/>
       <c r="AI384"/>
     </row>
-    <row r="385" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A385" s="72">
         <v>556</v>
       </c>
@@ -43926,7 +44061,7 @@
       <c r="AH385"/>
       <c r="AI385"/>
     </row>
-    <row r="386" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A386" s="72">
         <v>333</v>
       </c>
@@ -43964,13 +44099,13 @@
       <c r="L386" s="52" t="s">
         <v>875</v>
       </c>
-      <c r="M386" s="6">
+      <c r="M386" s="6" t="e">
         <f t="shared" ref="M386:M445" si="30">I386-(H386+J386-K386)-L386</f>
-        <v>1367550</v>
-      </c>
-      <c r="N386" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N386" s="21" t="e">
         <f t="shared" ref="N386:N445" si="31">IF(M386="","",IF(M386=0,"Cuadrado",IF(M386&gt;0,"Faltante","Sobrante")))</f>
-        <v>Faltante</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O386" s="13" t="s">
         <v>879</v>
@@ -43998,7 +44133,7 @@
       <c r="AH386"/>
       <c r="AI386"/>
     </row>
-    <row r="387" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A387" s="72">
         <v>331</v>
       </c>
@@ -44068,7 +44203,7 @@
       <c r="AH387"/>
       <c r="AI387"/>
     </row>
-    <row r="388" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A388" s="72">
         <v>907</v>
       </c>
@@ -44141,7 +44276,7 @@
       <c r="AH388"/>
       <c r="AI388"/>
     </row>
-    <row r="389" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A389" s="72">
         <v>59</v>
       </c>
@@ -44211,7 +44346,7 @@
       <c r="AH389"/>
       <c r="AI389"/>
     </row>
-    <row r="390" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A390" s="72">
         <v>907</v>
       </c>
@@ -44284,7 +44419,7 @@
       <c r="AH390"/>
       <c r="AI390"/>
     </row>
-    <row r="391" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A391" s="72">
         <v>882</v>
       </c>
@@ -44354,7 +44489,7 @@
       <c r="AH391"/>
       <c r="AI391"/>
     </row>
-    <row r="392" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A392" s="72">
         <v>824</v>
       </c>
@@ -44426,7 +44561,7 @@
       <c r="AH392"/>
       <c r="AI392"/>
     </row>
-    <row r="393" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A393" s="72">
         <v>879</v>
       </c>
@@ -44499,7 +44634,7 @@
       <c r="AH393"/>
       <c r="AI393"/>
     </row>
-    <row r="394" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A394" s="72">
         <v>723</v>
       </c>
@@ -44571,7 +44706,7 @@
       <c r="AH394"/>
       <c r="AI394"/>
     </row>
-    <row r="395" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A395" s="72">
         <v>261</v>
       </c>
@@ -44641,7 +44776,7 @@
       <c r="AH395"/>
       <c r="AI395"/>
     </row>
-    <row r="396" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A396" s="72">
         <v>916</v>
       </c>
@@ -44711,7 +44846,7 @@
       <c r="AH396"/>
       <c r="AI396"/>
     </row>
-    <row r="397" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A397" s="72">
         <v>652</v>
       </c>
@@ -44781,7 +44916,7 @@
       <c r="AH397"/>
       <c r="AI397"/>
     </row>
-    <row r="398" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A398" s="72">
         <v>265</v>
       </c>
@@ -44851,7 +44986,7 @@
       <c r="AH398"/>
       <c r="AI398"/>
     </row>
-    <row r="399" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A399" s="72">
         <v>197</v>
       </c>
@@ -44923,7 +45058,7 @@
       <c r="AH399"/>
       <c r="AI399"/>
     </row>
-    <row r="400" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A400" s="72">
         <v>634</v>
       </c>
@@ -44996,7 +45131,7 @@
       <c r="AH400"/>
       <c r="AI400"/>
     </row>
-    <row r="401" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A401" s="72">
         <v>88</v>
       </c>
@@ -45066,7 +45201,7 @@
       <c r="AH401"/>
       <c r="AI401"/>
     </row>
-    <row r="402" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A402" s="72">
         <v>291</v>
       </c>
@@ -45138,7 +45273,7 @@
       <c r="AH402"/>
       <c r="AI402"/>
     </row>
-    <row r="403" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A403" s="72">
         <v>76</v>
       </c>
@@ -45210,7 +45345,7 @@
       <c r="AH403"/>
       <c r="AI403"/>
     </row>
-    <row r="404" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A404" s="72">
         <v>829</v>
       </c>
@@ -45282,7 +45417,7 @@
       <c r="AH404"/>
       <c r="AI404"/>
     </row>
-    <row r="405" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A405" s="72">
         <v>258</v>
       </c>
@@ -45352,7 +45487,7 @@
       <c r="AH405"/>
       <c r="AI405"/>
     </row>
-    <row r="406" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A406" s="72">
         <v>70</v>
       </c>
@@ -45425,7 +45560,7 @@
       <c r="AH406"/>
       <c r="AI406"/>
     </row>
-    <row r="407" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A407" s="72">
         <v>420</v>
       </c>
@@ -45495,7 +45630,7 @@
       <c r="AH407"/>
       <c r="AI407"/>
     </row>
-    <row r="408" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A408" s="72">
         <v>198</v>
       </c>
@@ -45568,7 +45703,7 @@
       <c r="AH408"/>
       <c r="AI408"/>
     </row>
-    <row r="409" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A409" s="72">
         <v>383</v>
       </c>
@@ -45638,7 +45773,7 @@
       <c r="AH409"/>
       <c r="AI409"/>
     </row>
-    <row r="410" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A410" s="72">
         <v>816</v>
       </c>
@@ -45708,7 +45843,7 @@
       <c r="AH410"/>
       <c r="AI410"/>
     </row>
-    <row r="411" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A411" s="72">
         <v>455</v>
       </c>
@@ -45778,7 +45913,7 @@
       <c r="AH411"/>
       <c r="AI411"/>
     </row>
-    <row r="412" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A412" s="72">
         <v>16</v>
       </c>
@@ -45850,7 +45985,7 @@
       <c r="AH412"/>
       <c r="AI412"/>
     </row>
-    <row r="413" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A413" s="72">
         <v>844</v>
       </c>
@@ -45888,13 +46023,13 @@
       <c r="L413" s="52" t="s">
         <v>878</v>
       </c>
-      <c r="M413" s="6">
+      <c r="M413" s="6" t="e">
         <f t="shared" si="30"/>
-        <v>-903200</v>
-      </c>
-      <c r="N413" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N413" s="21" t="e">
         <f t="shared" si="31"/>
-        <v>Sobrante</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O413" s="9" t="s">
         <v>880</v>
@@ -45922,7 +46057,7 @@
       <c r="AH413"/>
       <c r="AI413"/>
     </row>
-    <row r="414" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A414" s="72">
         <v>820</v>
       </c>
@@ -45994,7 +46129,7 @@
       <c r="AH414"/>
       <c r="AI414"/>
     </row>
-    <row r="415" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A415" s="72">
         <v>688</v>
       </c>
@@ -46066,7 +46201,7 @@
       <c r="AH415"/>
       <c r="AI415"/>
     </row>
-    <row r="416" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A416" s="72">
         <v>74</v>
       </c>
@@ -46138,7 +46273,7 @@
       <c r="AH416"/>
       <c r="AI416"/>
     </row>
-    <row r="417" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A417" s="72">
         <v>236</v>
       </c>
@@ -46208,7 +46343,7 @@
       <c r="AH417"/>
       <c r="AI417"/>
     </row>
-    <row r="418" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A418" s="72">
         <v>79</v>
       </c>
@@ -46280,7 +46415,7 @@
       <c r="AH418"/>
       <c r="AI418"/>
     </row>
-    <row r="419" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A419" s="72">
         <v>78</v>
       </c>
@@ -46353,7 +46488,7 @@
       <c r="AH419"/>
       <c r="AI419"/>
     </row>
-    <row r="420" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A420" s="72">
         <v>524</v>
       </c>
@@ -46423,7 +46558,7 @@
       <c r="AH420"/>
       <c r="AI420"/>
     </row>
-    <row r="421" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A421" s="72">
         <v>237</v>
       </c>
@@ -46496,7 +46631,7 @@
       <c r="AH421"/>
       <c r="AI421"/>
     </row>
-    <row r="422" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A422" s="72">
         <v>352</v>
       </c>
@@ -46568,7 +46703,7 @@
       <c r="AH422"/>
       <c r="AI422"/>
     </row>
-    <row r="423" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A423" s="72">
         <v>138</v>
       </c>
@@ -46638,7 +46773,7 @@
       <c r="AH423"/>
       <c r="AI423"/>
     </row>
-    <row r="424" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A424" s="72">
         <v>613</v>
       </c>
@@ -46710,7 +46845,7 @@
       <c r="AH424"/>
       <c r="AI424"/>
     </row>
-    <row r="425" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A425" s="72">
         <v>20</v>
       </c>
@@ -46783,7 +46918,7 @@
       <c r="AH425"/>
       <c r="AI425"/>
     </row>
-    <row r="426" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A426" s="72">
         <v>536</v>
       </c>
@@ -46855,7 +46990,7 @@
       <c r="AH426"/>
       <c r="AI426"/>
     </row>
-    <row r="427" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A427" s="72">
         <v>549</v>
       </c>
@@ -46925,7 +47060,7 @@
       <c r="AH427"/>
       <c r="AI427"/>
     </row>
-    <row r="428" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A428" s="72">
         <v>385</v>
       </c>
@@ -46997,7 +47132,7 @@
       <c r="AH428"/>
       <c r="AI428"/>
     </row>
-    <row r="429" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A429" s="72">
         <v>7</v>
       </c>
@@ -47035,13 +47170,13 @@
       <c r="L429" s="52" t="s">
         <v>876</v>
       </c>
-      <c r="M429" s="6">
+      <c r="M429" s="6" t="e">
         <f t="shared" si="30"/>
-        <v>710000</v>
-      </c>
-      <c r="N429" s="21" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N429" s="21" t="e">
         <f t="shared" si="31"/>
-        <v>Faltante</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O429" s="13" t="s">
         <v>879</v>
@@ -47069,7 +47204,7 @@
       <c r="AH429"/>
       <c r="AI429"/>
     </row>
-    <row r="430" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A430" s="72">
         <v>693</v>
       </c>
@@ -47141,7 +47276,7 @@
       <c r="AH430"/>
       <c r="AI430"/>
     </row>
-    <row r="431" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A431" s="72">
         <v>554</v>
       </c>
@@ -47214,7 +47349,7 @@
       <c r="AH431"/>
       <c r="AI431"/>
     </row>
-    <row r="432" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A432" s="72">
         <v>554</v>
       </c>
@@ -47284,7 +47419,7 @@
       <c r="AH432"/>
       <c r="AI432"/>
     </row>
-    <row r="433" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A433" s="72">
         <v>236</v>
       </c>
@@ -47354,7 +47489,7 @@
       <c r="AH433"/>
       <c r="AI433"/>
     </row>
-    <row r="434" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A434" s="72">
         <v>78</v>
       </c>
@@ -47427,7 +47562,7 @@
       <c r="AH434"/>
       <c r="AI434"/>
     </row>
-    <row r="435" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A435" s="72">
         <v>866</v>
       </c>
@@ -47497,7 +47632,7 @@
       <c r="AH435"/>
       <c r="AI435"/>
     </row>
-    <row r="436" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A436" s="72">
         <v>721</v>
       </c>
@@ -47567,7 +47702,7 @@
       <c r="AH436"/>
       <c r="AI436"/>
     </row>
-    <row r="437" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A437" s="72">
         <v>20</v>
       </c>
@@ -47640,7 +47775,7 @@
       <c r="AH437"/>
       <c r="AI437"/>
     </row>
-    <row r="438" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A438" s="72">
         <v>536</v>
       </c>
@@ -47710,7 +47845,7 @@
       <c r="AH438"/>
       <c r="AI438"/>
     </row>
-    <row r="439" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A439" s="72">
         <v>20</v>
       </c>
@@ -47783,7 +47918,7 @@
       <c r="AH439"/>
       <c r="AI439"/>
     </row>
-    <row r="440" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A440" s="72">
         <v>845</v>
       </c>
@@ -47855,7 +47990,7 @@
       <c r="AH440"/>
       <c r="AI440"/>
     </row>
-    <row r="441" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A441" s="72">
         <v>367</v>
       </c>
@@ -47925,7 +48060,7 @@
       <c r="AH441"/>
       <c r="AI441"/>
     </row>
-    <row r="442" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A442" s="72">
         <v>229</v>
       </c>
@@ -47995,7 +48130,7 @@
       <c r="AH442"/>
       <c r="AI442"/>
     </row>
-    <row r="443" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A443" s="72">
         <v>551</v>
       </c>
@@ -48065,7 +48200,7 @@
       <c r="AH443"/>
       <c r="AI443"/>
     </row>
-    <row r="444" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A444" s="72">
         <v>849</v>
       </c>
@@ -48135,7 +48270,7 @@
       <c r="AH444"/>
       <c r="AI444"/>
     </row>
-    <row r="445" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A445" s="72">
         <v>499</v>
       </c>
@@ -48205,7 +48340,7 @@
       <c r="AH445"/>
       <c r="AI445"/>
     </row>
-    <row r="446" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A446" s="72">
         <v>377</v>
       </c>
@@ -48275,7 +48410,7 @@
       <c r="AH446"/>
       <c r="AI446"/>
     </row>
-    <row r="447" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A447" s="72">
         <v>333</v>
       </c>
@@ -48345,7 +48480,7 @@
       <c r="AH447"/>
       <c r="AI447"/>
     </row>
-    <row r="448" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A448" s="72">
         <v>115</v>
       </c>
@@ -48415,7 +48550,7 @@
       <c r="AH448"/>
       <c r="AI448"/>
     </row>
-    <row r="449" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A449" s="72">
         <v>743</v>
       </c>
@@ -48485,7 +48620,7 @@
       <c r="AH449"/>
       <c r="AI449"/>
     </row>
-    <row r="450" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A450" s="72">
         <v>674</v>
       </c>
@@ -48558,7 +48693,7 @@
       <c r="AH450"/>
       <c r="AI450"/>
     </row>
-    <row r="451" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A451" s="72">
         <v>606</v>
       </c>
@@ -48628,7 +48763,7 @@
       <c r="AH451"/>
       <c r="AI451"/>
     </row>
-    <row r="452" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A452" s="72">
         <v>371</v>
       </c>
@@ -48701,7 +48836,7 @@
       <c r="AH452"/>
       <c r="AI452"/>
     </row>
-    <row r="453" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A453" s="72">
         <v>233</v>
       </c>
@@ -48771,7 +48906,7 @@
       <c r="AH453"/>
       <c r="AI453"/>
     </row>
-    <row r="454" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A454" s="72">
         <v>848</v>
       </c>
@@ -48841,7 +48976,7 @@
       <c r="AH454"/>
       <c r="AI454"/>
     </row>
-    <row r="455" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A455" s="72">
         <v>728</v>
       </c>
@@ -48911,7 +49046,7 @@
       <c r="AH455"/>
       <c r="AI455"/>
     </row>
-    <row r="456" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A456" s="72">
         <v>728</v>
       </c>
@@ -48981,7 +49116,7 @@
       <c r="AH456"/>
       <c r="AI456"/>
     </row>
-    <row r="457" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A457" s="72">
         <v>451</v>
       </c>
@@ -49051,7 +49186,7 @@
       <c r="AH457"/>
       <c r="AI457"/>
     </row>
-    <row r="458" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A458" s="72">
         <v>876</v>
       </c>
@@ -49121,7 +49256,7 @@
       <c r="AH458"/>
       <c r="AI458"/>
     </row>
-    <row r="459" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A459" s="72">
         <v>348</v>
       </c>
@@ -49191,7 +49326,7 @@
       <c r="AH459"/>
       <c r="AI459"/>
     </row>
-    <row r="460" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A460" s="72">
         <v>879</v>
       </c>
@@ -49264,7 +49399,7 @@
       <c r="AH460"/>
       <c r="AI460"/>
     </row>
-    <row r="461" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A461" s="72">
         <v>769</v>
       </c>
@@ -49337,7 +49472,7 @@
       <c r="AH461"/>
       <c r="AI461"/>
     </row>
-    <row r="462" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A462" s="72">
         <v>24</v>
       </c>
@@ -49410,7 +49545,7 @@
       <c r="AH462"/>
       <c r="AI462"/>
     </row>
-    <row r="463" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A463" s="72">
         <v>789</v>
       </c>
@@ -49477,7 +49612,7 @@
       <c r="AH463"/>
       <c r="AI463"/>
     </row>
-    <row r="464" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A464" s="72">
         <v>667</v>
       </c>
@@ -49549,7 +49684,7 @@
       <c r="AH464"/>
       <c r="AI464"/>
     </row>
-    <row r="465" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A465" s="72">
         <v>698</v>
       </c>
@@ -49619,7 +49754,7 @@
       <c r="AH465"/>
       <c r="AI465"/>
     </row>
-    <row r="466" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A466" s="72">
         <v>674</v>
       </c>
@@ -49691,7 +49826,7 @@
       <c r="AH466"/>
       <c r="AI466"/>
     </row>
-    <row r="467" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A467" s="72">
         <v>178</v>
       </c>
@@ -49764,7 +49899,7 @@
       <c r="AH467"/>
       <c r="AI467"/>
     </row>
-    <row r="468" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A468" s="72">
         <v>78</v>
       </c>
@@ -49837,7 +49972,7 @@
       <c r="AH468"/>
       <c r="AI468"/>
     </row>
-    <row r="469" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A469" s="72">
         <v>337</v>
       </c>
@@ -49907,7 +50042,7 @@
       <c r="AH469"/>
       <c r="AI469"/>
     </row>
-    <row r="470" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A470" s="72">
         <v>348</v>
       </c>
@@ -49980,7 +50115,7 @@
       <c r="AH470"/>
       <c r="AI470"/>
     </row>
-    <row r="471" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A471" s="72">
         <v>741</v>
       </c>
@@ -50050,7 +50185,7 @@
       <c r="AH471"/>
       <c r="AI471"/>
     </row>
-    <row r="472" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A472" s="72">
         <v>385</v>
       </c>
@@ -50122,7 +50257,7 @@
       <c r="AH472"/>
       <c r="AI472"/>
     </row>
-    <row r="473" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A473" s="72">
         <v>389</v>
       </c>
@@ -50192,7 +50327,7 @@
       <c r="AH473"/>
       <c r="AI473"/>
     </row>
-    <row r="474" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A474" s="72">
         <v>453</v>
       </c>
@@ -50264,7 +50399,7 @@
       <c r="AH474"/>
       <c r="AI474"/>
     </row>
-    <row r="475" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A475" s="72">
         <v>453</v>
       </c>
@@ -50337,7 +50472,7 @@
       <c r="AH475"/>
       <c r="AI475"/>
     </row>
-    <row r="476" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A476" s="72">
         <v>556</v>
       </c>
@@ -50407,7 +50542,7 @@
       <c r="AH476"/>
       <c r="AI476"/>
     </row>
-    <row r="477" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A477" s="72">
         <v>769</v>
       </c>
@@ -50477,7 +50612,7 @@
       <c r="AH477"/>
       <c r="AI477"/>
     </row>
-    <row r="478" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A478" s="72">
         <v>60</v>
       </c>
@@ -50550,7 +50685,7 @@
       <c r="AH478"/>
       <c r="AI478"/>
     </row>
-    <row r="479" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A479" s="72">
         <v>60</v>
       </c>
@@ -50623,7 +50758,7 @@
       <c r="AH479"/>
       <c r="AI479"/>
     </row>
-    <row r="480" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A480" s="72">
         <v>33</v>
       </c>
@@ -50695,7 +50830,7 @@
       <c r="AH480"/>
       <c r="AI480"/>
     </row>
-    <row r="481" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A481" s="72">
         <v>225</v>
       </c>
@@ -50765,7 +50900,7 @@
       <c r="AH481"/>
       <c r="AI481"/>
     </row>
-    <row r="482" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A482" s="72">
         <v>225</v>
       </c>
@@ -50838,7 +50973,7 @@
       <c r="AH482"/>
       <c r="AI482"/>
     </row>
-    <row r="483" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A483" s="72">
         <v>457</v>
       </c>
@@ -50910,7 +51045,7 @@
       <c r="AH483"/>
       <c r="AI483"/>
     </row>
-    <row r="484" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A484" s="72">
         <v>348</v>
       </c>
@@ -50980,7 +51115,7 @@
       <c r="AH484"/>
       <c r="AI484"/>
     </row>
-    <row r="485" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A485" s="72">
         <v>467</v>
       </c>
@@ -51050,7 +51185,7 @@
       <c r="AH485"/>
       <c r="AI485"/>
     </row>
-    <row r="486" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A486" s="72">
         <v>467</v>
       </c>
@@ -51120,7 +51255,7 @@
       <c r="AH486"/>
       <c r="AI486"/>
     </row>
-    <row r="487" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A487" s="72">
         <v>551</v>
       </c>
@@ -51190,7 +51325,7 @@
       <c r="AH487"/>
       <c r="AI487"/>
     </row>
-    <row r="488" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A488" s="72">
         <v>516</v>
       </c>
@@ -51262,7 +51397,7 @@
       <c r="AH488"/>
       <c r="AI488"/>
     </row>
-    <row r="489" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A489" s="72">
         <v>511</v>
       </c>
@@ -51332,7 +51467,7 @@
       <c r="AH489"/>
       <c r="AI489"/>
     </row>
-    <row r="490" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A490" s="72">
         <v>300</v>
       </c>
@@ -51402,7 +51537,7 @@
       <c r="AH490"/>
       <c r="AI490"/>
     </row>
-    <row r="491" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A491" s="72">
         <v>718</v>
       </c>
@@ -51472,7 +51607,7 @@
       <c r="AH491"/>
       <c r="AI491"/>
     </row>
-    <row r="492" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A492" s="72">
         <v>37</v>
       </c>
@@ -51542,7 +51677,7 @@
       <c r="AH492"/>
       <c r="AI492"/>
     </row>
-    <row r="493" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A493" s="72">
         <v>728</v>
       </c>
@@ -51612,7 +51747,7 @@
       <c r="AH493"/>
       <c r="AI493"/>
     </row>
-    <row r="494" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A494" s="72">
         <v>728</v>
       </c>
@@ -51682,7 +51817,7 @@
       <c r="AH494"/>
       <c r="AI494"/>
     </row>
-    <row r="495" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A495" s="88">
         <v>115</v>
       </c>
@@ -51752,7 +51887,7 @@
       <c r="AH495"/>
       <c r="AI495"/>
     </row>
-    <row r="496" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A496" s="72">
         <v>88</v>
       </c>
@@ -51822,7 +51957,7 @@
       <c r="AH496"/>
       <c r="AI496"/>
     </row>
-    <row r="497" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A497" s="72">
         <v>70</v>
       </c>
@@ -51892,7 +52027,7 @@
       <c r="AH497"/>
       <c r="AI497"/>
     </row>
-    <row r="498" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A498" s="88">
         <v>432</v>
       </c>
@@ -51962,7 +52097,7 @@
       <c r="AH498"/>
       <c r="AI498"/>
     </row>
-    <row r="499" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A499" s="88">
         <v>674</v>
       </c>
@@ -52034,7 +52169,7 @@
       <c r="AH499"/>
       <c r="AI499"/>
     </row>
-    <row r="500" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A500" s="88">
         <v>606</v>
       </c>
@@ -52104,7 +52239,7 @@
       <c r="AH500"/>
       <c r="AI500"/>
     </row>
-    <row r="501" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A501" s="72">
         <v>455</v>
       </c>
@@ -52174,7 +52309,7 @@
       <c r="AH501"/>
       <c r="AI501"/>
     </row>
-    <row r="502" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A502" s="72">
         <v>74</v>
       </c>
@@ -52244,7 +52379,7 @@
       <c r="AH502"/>
       <c r="AI502"/>
     </row>
-    <row r="503" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A503" s="88">
         <v>236</v>
       </c>
@@ -52316,7 +52451,7 @@
       <c r="AH503"/>
       <c r="AI503"/>
     </row>
-    <row r="504" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A504" s="72">
         <v>317</v>
       </c>
@@ -52386,7 +52521,7 @@
       <c r="AH504"/>
       <c r="AI504"/>
     </row>
-    <row r="505" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A505" s="72">
         <v>442</v>
       </c>
@@ -52456,7 +52591,7 @@
       <c r="AH505"/>
       <c r="AI505"/>
     </row>
-    <row r="506" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A506" s="72">
         <v>959</v>
       </c>
@@ -52526,7 +52661,7 @@
       <c r="AH506"/>
       <c r="AI506"/>
     </row>
-    <row r="507" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A507" s="72">
         <v>383</v>
       </c>
@@ -52598,7 +52733,7 @@
       <c r="AH507"/>
       <c r="AI507"/>
     </row>
-    <row r="508" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A508" s="72">
         <v>728</v>
       </c>
@@ -52668,7 +52803,7 @@
       <c r="AH508"/>
       <c r="AI508"/>
     </row>
-    <row r="509" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A509" s="72">
         <v>728</v>
       </c>
@@ -52738,7 +52873,7 @@
       <c r="AH509"/>
       <c r="AI509"/>
     </row>
-    <row r="510" spans="1:35" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:35" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A510" s="72">
         <v>890</v>
       </c>
@@ -52808,29 +52943,2430 @@
       <c r="AH510"/>
       <c r="AI510"/>
     </row>
-    <row r="517" spans="12:12" x14ac:dyDescent="0.35">
-      <c r="L517" s="90"/>
-    </row>
-    <row r="518" spans="12:12" x14ac:dyDescent="0.35">
-      <c r="L518" s="90"/>
-    </row>
-    <row r="519" spans="12:12" x14ac:dyDescent="0.35">
-      <c r="L519" s="90"/>
-    </row>
-    <row r="520" spans="12:12" x14ac:dyDescent="0.35">
-      <c r="L520" s="90"/>
-    </row>
-    <row r="521" spans="12:12" x14ac:dyDescent="0.35">
-      <c r="L521" s="90"/>
+    <row r="511" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A511" s="90">
+        <v>61</v>
+      </c>
+      <c r="B511" s="90">
+        <v>788</v>
+      </c>
+      <c r="C511" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D511" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E511" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F511" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G511" s="92">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="H511" s="93">
+        <v>205975550</v>
+      </c>
+      <c r="I511" s="93">
+        <v>203455550</v>
+      </c>
+      <c r="J511" s="93">
+        <v>1430000</v>
+      </c>
+      <c r="K511" s="93">
+        <v>2000000</v>
+      </c>
+      <c r="L511" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M511" s="93">
+        <v>-1950000</v>
+      </c>
+      <c r="N511" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O511" s="90"/>
+      <c r="P511" s="90">
+        <v>16497924</v>
+      </c>
+      <c r="Q511" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R511" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S511" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="512" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A512" s="90">
+        <v>287</v>
+      </c>
+      <c r="B512" s="90">
+        <v>907</v>
+      </c>
+      <c r="C512" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D512" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E512" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F512" s="91">
+        <v>46097</v>
+      </c>
+      <c r="G512" s="92">
+        <v>0.62916666666666665</v>
+      </c>
+      <c r="H512" s="93">
+        <v>153313650</v>
+      </c>
+      <c r="I512" s="93">
+        <v>165008750</v>
+      </c>
+      <c r="J512" s="93">
+        <v>32730000</v>
+      </c>
+      <c r="K512" s="93">
+        <v>3020000</v>
+      </c>
+      <c r="L512" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M512" s="93">
+        <v>-18014900</v>
+      </c>
+      <c r="N512" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O512" s="90"/>
+      <c r="P512" s="90">
+        <v>13566403</v>
+      </c>
+      <c r="Q512" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R512" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S512" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="513" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A513" s="90">
+        <v>395</v>
+      </c>
+      <c r="B513" s="90">
+        <v>1529</v>
+      </c>
+      <c r="C513" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D513" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E513" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F513" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G513" s="92">
+        <v>0.40625</v>
+      </c>
+      <c r="H513" s="93">
+        <v>211457000</v>
+      </c>
+      <c r="I513" s="93">
+        <v>207047000</v>
+      </c>
+      <c r="J513" s="93">
+        <v>5610000</v>
+      </c>
+      <c r="K513" s="93">
+        <v>220000</v>
+      </c>
+      <c r="L513" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M513" s="93">
+        <v>-9800000</v>
+      </c>
+      <c r="N513" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O513" s="90"/>
+      <c r="P513" s="90">
+        <v>1121857901</v>
+      </c>
+      <c r="Q513" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R513" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S513" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="514" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A514" s="90">
+        <v>141</v>
+      </c>
+      <c r="B514" s="90">
+        <v>1541</v>
+      </c>
+      <c r="C514" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D514" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E514" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F514" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G514" s="92">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="H514" s="93">
+        <v>155925150</v>
+      </c>
+      <c r="I514" s="93">
+        <v>153311650</v>
+      </c>
+      <c r="J514" s="93">
+        <v>12470000</v>
+      </c>
+      <c r="K514" s="93">
+        <v>14405000</v>
+      </c>
+      <c r="L514" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M514" s="93">
+        <v>-678500</v>
+      </c>
+      <c r="N514" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O514" s="90"/>
+      <c r="P514" s="90">
+        <v>11225738</v>
+      </c>
+      <c r="Q514" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R514" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S514" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="515" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A515" s="90">
+        <v>944</v>
+      </c>
+      <c r="B515" s="90">
+        <v>2228</v>
+      </c>
+      <c r="C515" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D515" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E515" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F515" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G515" s="92">
+        <v>0.39513888888888887</v>
+      </c>
+      <c r="H515" s="93">
+        <v>331942550</v>
+      </c>
+      <c r="I515" s="93">
+        <v>327005900</v>
+      </c>
+      <c r="J515" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="K515" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="L515" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M515" s="93">
+        <v>-4936650</v>
+      </c>
+      <c r="N515" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O515" s="90"/>
+      <c r="P515" s="90">
+        <v>79644034</v>
+      </c>
+      <c r="Q515" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R515" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S515" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="516" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A516" s="90">
+        <v>723</v>
+      </c>
+      <c r="B516" s="90">
+        <v>5046</v>
+      </c>
+      <c r="C516" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D516" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E516" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F516" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G516" s="92">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="H516" s="93">
+        <v>181772500</v>
+      </c>
+      <c r="I516" s="93">
+        <v>128155500</v>
+      </c>
+      <c r="J516" s="93">
+        <v>57100000</v>
+      </c>
+      <c r="K516" s="93">
+        <v>94038000</v>
+      </c>
+      <c r="L516" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M516" s="93">
+        <v>-16679000</v>
+      </c>
+      <c r="N516" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O516" s="90"/>
+      <c r="P516" s="90">
+        <v>1036959981</v>
+      </c>
+      <c r="Q516" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R516" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S516" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="517" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A517" s="90">
+        <v>682</v>
+      </c>
+      <c r="B517" s="90">
+        <v>5049</v>
+      </c>
+      <c r="C517" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D517" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E517" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F517" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G517" s="92">
+        <v>0.38819444444444445</v>
+      </c>
+      <c r="H517" s="93">
+        <v>225384050</v>
+      </c>
+      <c r="I517" s="93">
+        <v>217768850</v>
+      </c>
+      <c r="J517" s="93">
+        <v>4990000</v>
+      </c>
+      <c r="K517" s="93">
+        <v>9685000</v>
+      </c>
+      <c r="L517" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M517" s="93">
+        <v>-2920200</v>
+      </c>
+      <c r="N517" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O517" s="90"/>
+      <c r="P517" s="90">
+        <v>1018447800</v>
+      </c>
+      <c r="Q517" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R517" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S517" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="518" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A518" s="90">
+        <v>24</v>
+      </c>
+      <c r="B518" s="90">
+        <v>5066</v>
+      </c>
+      <c r="C518" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D518" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E518" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F518" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G518" s="92">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="H518" s="93">
+        <v>216243300</v>
+      </c>
+      <c r="I518" s="93">
+        <v>213070650</v>
+      </c>
+      <c r="J518" s="93">
+        <v>370000</v>
+      </c>
+      <c r="K518" s="93">
+        <v>3515000</v>
+      </c>
+      <c r="L518" s="93">
+        <v>-27650</v>
+      </c>
+      <c r="M518" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N518" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O518" s="90" t="s">
+        <v>964</v>
+      </c>
+      <c r="P518" s="90">
+        <v>39447263</v>
+      </c>
+      <c r="Q518" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R518" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S518" s="90" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="519" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A519" s="90">
+        <v>652</v>
+      </c>
+      <c r="B519" s="90">
+        <v>5070</v>
+      </c>
+      <c r="C519" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D519" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E519" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F519" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G519" s="92">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="H519" s="93">
+        <v>209863600</v>
+      </c>
+      <c r="I519" s="93">
+        <v>203457350</v>
+      </c>
+      <c r="J519" s="93">
+        <v>5780000</v>
+      </c>
+      <c r="K519" s="93">
+        <v>12726500</v>
+      </c>
+      <c r="L519" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M519" s="93">
+        <v>540250</v>
+      </c>
+      <c r="N519" s="90" t="s">
+        <v>967</v>
+      </c>
+      <c r="O519" s="90"/>
+      <c r="P519" s="90">
+        <v>1010190714</v>
+      </c>
+      <c r="Q519" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R519" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S519" s="90" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="520" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A520" s="90">
+        <v>333</v>
+      </c>
+      <c r="B520" s="90">
+        <v>5076</v>
+      </c>
+      <c r="C520" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D520" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E520" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F520" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G520" s="92">
+        <v>0.56458333333333333</v>
+      </c>
+      <c r="H520" s="93">
+        <v>61038650</v>
+      </c>
+      <c r="I520" s="93">
+        <v>204208650</v>
+      </c>
+      <c r="J520" s="93">
+        <v>6140000</v>
+      </c>
+      <c r="K520" s="93">
+        <v>7400000</v>
+      </c>
+      <c r="L520" s="93">
+        <v>151710000</v>
+      </c>
+      <c r="M520" s="93">
+        <v>-7280000</v>
+      </c>
+      <c r="N520" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O520" s="90"/>
+      <c r="P520" s="90">
+        <v>1036606819</v>
+      </c>
+      <c r="Q520" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R520" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S520" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="521" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A521" s="90">
+        <v>523</v>
+      </c>
+      <c r="B521" s="90">
+        <v>5082</v>
+      </c>
+      <c r="C521" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D521" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E521" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F521" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G521" s="92">
+        <v>0.37152777777777779</v>
+      </c>
+      <c r="H521" s="93">
+        <v>167425950</v>
+      </c>
+      <c r="I521" s="93">
+        <v>162426000</v>
+      </c>
+      <c r="J521" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="K521" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="L521" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M521" s="93">
+        <v>-4999950</v>
+      </c>
+      <c r="N521" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O521" s="90"/>
+      <c r="P521" s="90">
+        <v>1065609766</v>
+      </c>
+      <c r="Q521" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R521" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S521" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="522" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A522" s="90">
+        <v>73</v>
+      </c>
+      <c r="B522" s="90">
+        <v>5108</v>
+      </c>
+      <c r="C522" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D522" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E522" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F522" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G522" s="92">
+        <v>0.36554398148148148</v>
+      </c>
+      <c r="H522" s="93">
+        <v>52492050</v>
+      </c>
+      <c r="I522" s="93">
+        <v>40036050</v>
+      </c>
+      <c r="J522" s="93">
+        <v>2000000</v>
+      </c>
+      <c r="K522" s="93">
+        <v>6591000</v>
+      </c>
+      <c r="L522" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M522" s="93">
+        <v>-7865000</v>
+      </c>
+      <c r="N522" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O522" s="90"/>
+      <c r="P522" s="90">
+        <v>42157515</v>
+      </c>
+      <c r="Q522" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R522" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S522" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="523" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A523" s="90">
+        <v>829</v>
+      </c>
+      <c r="B523" s="90">
+        <v>5137</v>
+      </c>
+      <c r="C523" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D523" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E523" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F523" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G523" s="92">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="H523" s="93">
+        <v>264842300</v>
+      </c>
+      <c r="I523" s="93">
+        <v>261322300</v>
+      </c>
+      <c r="J523" s="93">
+        <v>590000</v>
+      </c>
+      <c r="K523" s="93">
+        <v>4100000</v>
+      </c>
+      <c r="L523" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M523" s="93">
+        <v>-10000</v>
+      </c>
+      <c r="N523" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O523" s="90"/>
+      <c r="P523" s="90">
+        <v>31306454</v>
+      </c>
+      <c r="Q523" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R523" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S523" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="524" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A524" s="90">
+        <v>279</v>
+      </c>
+      <c r="B524" s="90">
+        <v>5147</v>
+      </c>
+      <c r="C524" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D524" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E524" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F524" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G524" s="92">
+        <v>0.43125000000000002</v>
+      </c>
+      <c r="H524" s="93">
+        <v>164220600</v>
+      </c>
+      <c r="I524" s="93">
+        <v>163918600</v>
+      </c>
+      <c r="J524" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="K524" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="L524" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M524" s="93">
+        <v>-302000</v>
+      </c>
+      <c r="N524" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O524" s="90"/>
+      <c r="P524" s="90">
+        <v>42826913</v>
+      </c>
+      <c r="Q524" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R524" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S524" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="525" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A525" s="90">
+        <v>358</v>
+      </c>
+      <c r="B525" s="90">
+        <v>5149</v>
+      </c>
+      <c r="C525" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D525" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E525" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F525" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G525" s="92">
+        <v>0.41875000000000001</v>
+      </c>
+      <c r="H525" s="93">
+        <v>369948450</v>
+      </c>
+      <c r="I525" s="93">
+        <v>345906450</v>
+      </c>
+      <c r="J525" s="93">
+        <v>2100000</v>
+      </c>
+      <c r="K525" s="93">
+        <v>25150000</v>
+      </c>
+      <c r="L525" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M525" s="93">
+        <v>-992000</v>
+      </c>
+      <c r="N525" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O525" s="90"/>
+      <c r="P525" s="90">
+        <v>46456877</v>
+      </c>
+      <c r="Q525" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R525" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S525" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="526" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A526" s="90">
+        <v>756</v>
+      </c>
+      <c r="B526" s="90">
+        <v>5183</v>
+      </c>
+      <c r="C526" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D526" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E526" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F526" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G526" s="92">
+        <v>0.42777777777777776</v>
+      </c>
+      <c r="H526" s="93">
+        <v>172762350</v>
+      </c>
+      <c r="I526" s="93">
+        <v>168571200</v>
+      </c>
+      <c r="J526" s="93">
+        <v>6030000</v>
+      </c>
+      <c r="K526" s="93">
+        <v>13595100</v>
+      </c>
+      <c r="L526" s="93">
+        <v>3373950</v>
+      </c>
+      <c r="M526" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N526" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O526" s="90" t="s">
+        <v>969</v>
+      </c>
+      <c r="P526" s="90">
+        <v>1094912219</v>
+      </c>
+      <c r="Q526" s="94" t="s">
+        <v>970</v>
+      </c>
+      <c r="R526" s="90" t="s">
+        <v>971</v>
+      </c>
+      <c r="S526" s="90" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="527" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A527" s="90">
+        <v>698</v>
+      </c>
+      <c r="B527" s="90">
+        <v>5187</v>
+      </c>
+      <c r="C527" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D527" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E527" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F527" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G527" s="92">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="H527" s="93">
+        <v>155881650</v>
+      </c>
+      <c r="I527" s="93">
+        <v>139470650</v>
+      </c>
+      <c r="J527" s="93">
+        <v>10190000</v>
+      </c>
+      <c r="K527" s="93">
+        <v>16600000</v>
+      </c>
+      <c r="L527" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M527" s="93">
+        <v>-10001000</v>
+      </c>
+      <c r="N527" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O527" s="90"/>
+      <c r="P527" s="90">
+        <v>80177355</v>
+      </c>
+      <c r="Q527" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R527" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S527" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="528" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A528" s="90">
+        <v>383</v>
+      </c>
+      <c r="B528" s="90">
+        <v>5194</v>
+      </c>
+      <c r="C528" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D528" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E528" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F528" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G528" s="92">
+        <v>0.40128472222222222</v>
+      </c>
+      <c r="H528" s="93">
+        <v>150562200</v>
+      </c>
+      <c r="I528" s="93">
+        <v>152422200</v>
+      </c>
+      <c r="J528" s="93">
+        <v>12600000</v>
+      </c>
+      <c r="K528" s="93">
+        <v>13440000</v>
+      </c>
+      <c r="L528" s="93">
+        <v>2700000</v>
+      </c>
+      <c r="M528" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N528" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O528" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P528" s="90">
+        <v>1073160492</v>
+      </c>
+      <c r="Q528" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R528" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S528" s="90" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="529" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A529" s="90">
+        <v>432</v>
+      </c>
+      <c r="B529" s="90">
+        <v>5195</v>
+      </c>
+      <c r="C529" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D529" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E529" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F529" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G529" s="92">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="H529" s="93">
+        <v>222501750</v>
+      </c>
+      <c r="I529" s="93">
+        <v>183242750</v>
+      </c>
+      <c r="J529" s="93">
+        <v>21210000</v>
+      </c>
+      <c r="K529" s="93">
+        <v>63660000</v>
+      </c>
+      <c r="L529" s="93">
+        <v>3191000</v>
+      </c>
+      <c r="M529" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N529" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O529" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P529" s="90">
+        <v>71935844</v>
+      </c>
+      <c r="Q529" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R529" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S529" s="90" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="530" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A530" s="90">
+        <v>941</v>
+      </c>
+      <c r="B530" s="90">
+        <v>5220</v>
+      </c>
+      <c r="C530" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D530" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E530" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F530" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G530" s="92">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="H530" s="93">
+        <v>209349950</v>
+      </c>
+      <c r="I530" s="93">
+        <v>205893400</v>
+      </c>
+      <c r="J530" s="93">
+        <v>4160000</v>
+      </c>
+      <c r="K530" s="93">
+        <v>6540000</v>
+      </c>
+      <c r="L530" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M530" s="93">
+        <v>-1076550</v>
+      </c>
+      <c r="N530" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O530" s="90"/>
+      <c r="P530" s="90">
+        <v>1075228904</v>
+      </c>
+      <c r="Q530" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R530" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S530" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="531" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A531" s="90">
+        <v>946</v>
+      </c>
+      <c r="B531" s="90">
+        <v>5225</v>
+      </c>
+      <c r="C531" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D531" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E531" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F531" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G531" s="92">
+        <v>0.48472222222222222</v>
+      </c>
+      <c r="H531" s="93">
+        <v>321212350</v>
+      </c>
+      <c r="I531" s="93">
+        <v>348568350</v>
+      </c>
+      <c r="J531" s="93">
+        <v>34740000</v>
+      </c>
+      <c r="K531" s="93">
+        <v>7084000</v>
+      </c>
+      <c r="L531" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M531" s="93">
+        <v>-300000</v>
+      </c>
+      <c r="N531" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O531" s="90"/>
+      <c r="P531" s="90">
+        <v>20500181</v>
+      </c>
+      <c r="Q531" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R531" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S531" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="532" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A532" s="90">
+        <v>690</v>
+      </c>
+      <c r="B532" s="90">
+        <v>6180</v>
+      </c>
+      <c r="C532" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D532" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E532" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F532" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G532" s="92">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="H532" s="93">
+        <v>98424500</v>
+      </c>
+      <c r="I532" s="93">
+        <v>86719500</v>
+      </c>
+      <c r="J532" s="93">
+        <v>24560000</v>
+      </c>
+      <c r="K532" s="93">
+        <v>36755000</v>
+      </c>
+      <c r="L532" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M532" s="93">
+        <v>490000</v>
+      </c>
+      <c r="N532" s="90" t="s">
+        <v>967</v>
+      </c>
+      <c r="O532" s="90"/>
+      <c r="P532" s="90">
+        <v>1018459514</v>
+      </c>
+      <c r="Q532" s="94" t="s">
+        <v>970</v>
+      </c>
+      <c r="R532" s="90" t="s">
+        <v>973</v>
+      </c>
+      <c r="S532" s="90" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="533" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A533" s="90">
+        <v>601</v>
+      </c>
+      <c r="B533" s="90">
+        <v>6407</v>
+      </c>
+      <c r="C533" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D533" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E533" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F533" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G533" s="92">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="H533" s="93">
+        <v>213178650</v>
+      </c>
+      <c r="I533" s="93">
+        <v>158011150</v>
+      </c>
+      <c r="J533" s="93">
+        <v>8380000</v>
+      </c>
+      <c r="K533" s="93">
+        <v>63197000</v>
+      </c>
+      <c r="L533" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M533" s="93">
+        <v>-350500</v>
+      </c>
+      <c r="N533" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O533" s="90"/>
+      <c r="P533" s="90">
+        <v>1015399389</v>
+      </c>
+      <c r="Q533" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R533" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S533" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="534" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A534" s="90">
+        <v>202</v>
+      </c>
+      <c r="B534" s="90">
+        <v>6608</v>
+      </c>
+      <c r="C534" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D534" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E534" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F534" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G534" s="92">
+        <v>0.46944444444444444</v>
+      </c>
+      <c r="H534" s="93">
+        <v>192685150</v>
+      </c>
+      <c r="I534" s="93">
+        <v>186687550</v>
+      </c>
+      <c r="J534" s="93">
+        <v>13450000</v>
+      </c>
+      <c r="K534" s="93">
+        <v>28122700</v>
+      </c>
+      <c r="L534" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M534" s="93">
+        <v>8675100</v>
+      </c>
+      <c r="N534" s="90" t="s">
+        <v>967</v>
+      </c>
+      <c r="O534" s="90"/>
+      <c r="P534" s="90">
+        <v>1012330585</v>
+      </c>
+      <c r="Q534" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R534" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S534" s="90" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="535" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A535" s="90">
+        <v>613</v>
+      </c>
+      <c r="B535" s="90">
+        <v>6713</v>
+      </c>
+      <c r="C535" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D535" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E535" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F535" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G535" s="92">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="H535" s="93">
+        <v>226012350</v>
+      </c>
+      <c r="I535" s="93">
+        <v>223619350</v>
+      </c>
+      <c r="J535" s="93">
+        <v>4430000</v>
+      </c>
+      <c r="K535" s="93">
+        <v>4355000</v>
+      </c>
+      <c r="L535" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M535" s="93">
+        <v>-2468000</v>
+      </c>
+      <c r="N535" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O535" s="90"/>
+      <c r="P535" s="90">
+        <v>1040325060</v>
+      </c>
+      <c r="Q535" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R535" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S535" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="536" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A536" s="90">
+        <v>96</v>
+      </c>
+      <c r="B536" s="90">
+        <v>6735</v>
+      </c>
+      <c r="C536" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D536" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E536" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F536" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G536" s="92">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="H536" s="93">
+        <v>149452450</v>
+      </c>
+      <c r="I536" s="93">
+        <v>157094450</v>
+      </c>
+      <c r="J536" s="93">
+        <v>24790000</v>
+      </c>
+      <c r="K536" s="93">
+        <v>18960000</v>
+      </c>
+      <c r="L536" s="93">
+        <v>1812000</v>
+      </c>
+      <c r="M536" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N536" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O536" s="90" t="s">
+        <v>975</v>
+      </c>
+      <c r="P536" s="90">
+        <v>39491642</v>
+      </c>
+      <c r="Q536" s="94" t="s">
+        <v>970</v>
+      </c>
+      <c r="R536" s="90" t="s">
+        <v>976</v>
+      </c>
+      <c r="S536" s="90" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="537" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A537" s="90">
+        <v>796</v>
+      </c>
+      <c r="B537" s="90">
+        <v>6911</v>
+      </c>
+      <c r="C537" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D537" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E537" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F537" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G537" s="92">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="H537" s="93">
+        <v>163629850</v>
+      </c>
+      <c r="I537" s="93">
+        <v>157429850</v>
+      </c>
+      <c r="J537" s="93">
+        <v>610000</v>
+      </c>
+      <c r="K537" s="93">
+        <v>7400000</v>
+      </c>
+      <c r="L537" s="93">
+        <v>590000</v>
+      </c>
+      <c r="M537" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N537" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O537" s="90" t="s">
+        <v>978</v>
+      </c>
+      <c r="P537" s="90">
+        <v>1095802301</v>
+      </c>
+      <c r="Q537" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R537" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S537" s="90" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="538" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A538" s="90">
+        <v>385</v>
+      </c>
+      <c r="B538" s="90">
+        <v>7139</v>
+      </c>
+      <c r="C538" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D538" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E538" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F538" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G538" s="92">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="H538" s="93">
+        <v>200605850</v>
+      </c>
+      <c r="I538" s="93">
+        <v>208583850</v>
+      </c>
+      <c r="J538" s="93">
+        <v>30860000</v>
+      </c>
+      <c r="K538" s="93">
+        <v>13482000</v>
+      </c>
+      <c r="L538" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M538" s="93">
+        <v>-9400000</v>
+      </c>
+      <c r="N538" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O538" s="90"/>
+      <c r="P538" s="90">
+        <v>1077970238</v>
+      </c>
+      <c r="Q538" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R538" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S538" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="539" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A539" s="90">
+        <v>609</v>
+      </c>
+      <c r="B539" s="90">
+        <v>7875</v>
+      </c>
+      <c r="C539" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D539" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E539" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F539" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G539" s="92">
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="H539" s="93">
+        <v>99185350</v>
+      </c>
+      <c r="I539" s="93">
+        <v>122411650</v>
+      </c>
+      <c r="J539" s="93">
+        <v>33090000</v>
+      </c>
+      <c r="K539" s="93">
+        <v>10830700</v>
+      </c>
+      <c r="L539" s="93">
+        <v>967000</v>
+      </c>
+      <c r="M539" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N539" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O539" s="90" t="s">
+        <v>980</v>
+      </c>
+      <c r="P539" s="90">
+        <v>98695047</v>
+      </c>
+      <c r="Q539" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R539" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S539" s="90" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="540" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A540" s="90">
+        <v>609</v>
+      </c>
+      <c r="B540" s="90">
+        <v>7888</v>
+      </c>
+      <c r="C540" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D540" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E540" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F540" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G540" s="92">
+        <v>0.39027777777777778</v>
+      </c>
+      <c r="H540" s="93">
+        <v>212465400</v>
+      </c>
+      <c r="I540" s="93">
+        <v>254542400</v>
+      </c>
+      <c r="J540" s="93">
+        <v>44720000</v>
+      </c>
+      <c r="K540" s="93">
+        <v>6334000</v>
+      </c>
+      <c r="L540" s="93">
+        <v>3691000</v>
+      </c>
+      <c r="M540" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N540" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O540" s="90" t="s">
+        <v>982</v>
+      </c>
+      <c r="P540" s="90">
+        <v>98695047</v>
+      </c>
+      <c r="Q540" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R540" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S540" s="90" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="541" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A541" s="90">
+        <v>725</v>
+      </c>
+      <c r="B541" s="90">
+        <v>8090</v>
+      </c>
+      <c r="C541" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D541" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E541" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F541" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G541" s="92">
+        <v>0.62083333333333335</v>
+      </c>
+      <c r="H541" s="93">
+        <v>48931700</v>
+      </c>
+      <c r="I541" s="93">
+        <v>62258200</v>
+      </c>
+      <c r="J541" s="93">
+        <v>21840000</v>
+      </c>
+      <c r="K541" s="93">
+        <v>9108500</v>
+      </c>
+      <c r="L541" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M541" s="93">
+        <v>595000</v>
+      </c>
+      <c r="N541" s="90" t="s">
+        <v>967</v>
+      </c>
+      <c r="O541" s="90"/>
+      <c r="P541" s="90">
+        <v>1093220078</v>
+      </c>
+      <c r="Q541" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R541" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S541" s="90" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="542" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A542" s="90">
+        <v>944</v>
+      </c>
+      <c r="B542" s="90">
+        <v>8353</v>
+      </c>
+      <c r="C542" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D542" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E542" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F542" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G542" s="92">
+        <v>0.42638888888888887</v>
+      </c>
+      <c r="H542" s="93">
+        <v>208215300</v>
+      </c>
+      <c r="I542" s="93">
+        <v>153647300</v>
+      </c>
+      <c r="J542" s="93">
+        <v>2970000</v>
+      </c>
+      <c r="K542" s="93">
+        <v>41482000</v>
+      </c>
+      <c r="L542" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M542" s="93">
+        <v>-16056000</v>
+      </c>
+      <c r="N542" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O542" s="90"/>
+      <c r="P542" s="90">
+        <v>79644034</v>
+      </c>
+      <c r="Q542" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R542" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S542" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="543" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A543" s="90">
+        <v>944</v>
+      </c>
+      <c r="B543" s="90">
+        <v>8354</v>
+      </c>
+      <c r="C543" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D543" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E543" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F543" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G543" s="92">
+        <v>0.45069444444444445</v>
+      </c>
+      <c r="H543" s="93">
+        <v>279964850</v>
+      </c>
+      <c r="I543" s="93">
+        <v>236076800</v>
+      </c>
+      <c r="J543" s="93">
+        <v>5470000</v>
+      </c>
+      <c r="K543" s="93">
+        <v>50012650</v>
+      </c>
+      <c r="L543" s="93">
+        <v>654600</v>
+      </c>
+      <c r="M543" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N543" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O543" s="90" t="s">
+        <v>984</v>
+      </c>
+      <c r="P543" s="90">
+        <v>79644034</v>
+      </c>
+      <c r="Q543" s="94" t="s">
+        <v>970</v>
+      </c>
+      <c r="R543" s="90" t="s">
+        <v>985</v>
+      </c>
+      <c r="S543" s="90" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="544" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A544" s="90">
+        <v>31</v>
+      </c>
+      <c r="B544" s="90">
+        <v>8737</v>
+      </c>
+      <c r="C544" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D544" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E544" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F544" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G544" s="92">
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="H544" s="93">
+        <v>268667900</v>
+      </c>
+      <c r="I544" s="93">
+        <v>227784800</v>
+      </c>
+      <c r="J544" s="93">
+        <v>21080000</v>
+      </c>
+      <c r="K544" s="93">
+        <v>63093050</v>
+      </c>
+      <c r="L544" s="93">
+        <v>-260050</v>
+      </c>
+      <c r="M544" s="93">
+        <v>1390000</v>
+      </c>
+      <c r="N544" s="90" t="s">
+        <v>967</v>
+      </c>
+      <c r="O544" s="90"/>
+      <c r="P544" s="90">
+        <v>80168704</v>
+      </c>
+      <c r="Q544" s="94" t="s">
+        <v>970</v>
+      </c>
+      <c r="R544" s="90" t="s">
+        <v>973</v>
+      </c>
+      <c r="S544" s="90" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="545" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A545" s="90">
+        <v>33</v>
+      </c>
+      <c r="B545" s="90">
+        <v>8861</v>
+      </c>
+      <c r="C545" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D545" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E545" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F545" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G545" s="92">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="H545" s="93">
+        <v>230110250</v>
+      </c>
+      <c r="I545" s="93">
+        <v>219355250</v>
+      </c>
+      <c r="J545" s="93">
+        <v>4090000</v>
+      </c>
+      <c r="K545" s="93">
+        <v>5000000</v>
+      </c>
+      <c r="L545" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M545" s="93">
+        <v>-9845000</v>
+      </c>
+      <c r="N545" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O545" s="90"/>
+      <c r="P545" s="90">
+        <v>79659379</v>
+      </c>
+      <c r="Q545" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R545" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S545" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="546" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A546" s="90">
+        <v>225</v>
+      </c>
+      <c r="B546" s="90">
+        <v>8869</v>
+      </c>
+      <c r="C546" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D546" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E546" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F546" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G546" s="92">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="H546" s="93">
+        <v>160962450</v>
+      </c>
+      <c r="I546" s="93">
+        <v>298943450</v>
+      </c>
+      <c r="J546" s="93">
+        <v>21210000</v>
+      </c>
+      <c r="K546" s="93">
+        <v>35095000</v>
+      </c>
+      <c r="L546" s="93">
+        <v>161236000</v>
+      </c>
+      <c r="M546" s="93">
+        <v>-9370000</v>
+      </c>
+      <c r="N546" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O546" s="90"/>
+      <c r="P546" s="90">
+        <v>80212698</v>
+      </c>
+      <c r="Q546" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R546" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S546" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="547" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A547" s="90">
+        <v>64</v>
+      </c>
+      <c r="B547" s="90">
+        <v>9306</v>
+      </c>
+      <c r="C547" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D547" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E547" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F547" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G547" s="92">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="H547" s="93">
+        <v>206949650</v>
+      </c>
+      <c r="I547" s="93">
+        <v>221375650</v>
+      </c>
+      <c r="J547" s="93">
+        <v>29670000</v>
+      </c>
+      <c r="K547" s="93">
+        <v>11410000</v>
+      </c>
+      <c r="L547" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M547" s="93">
+        <v>-3834000</v>
+      </c>
+      <c r="N547" s="90" t="s">
+        <v>959</v>
+      </c>
+      <c r="O547" s="90"/>
+      <c r="P547" s="90">
+        <v>1144157313</v>
+      </c>
+      <c r="Q547" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R547" s="90" t="s">
+        <v>961</v>
+      </c>
+      <c r="S547" s="90" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="548" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A548" s="90">
+        <v>292</v>
+      </c>
+      <c r="B548" s="90">
+        <v>278</v>
+      </c>
+      <c r="C548" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D548" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E548" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F548" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G548" s="92">
+        <v>0.44513888888888886</v>
+      </c>
+      <c r="H548" s="93">
+        <v>108639700</v>
+      </c>
+      <c r="I548" s="93">
+        <v>119010700</v>
+      </c>
+      <c r="J548" s="93">
+        <v>15080000</v>
+      </c>
+      <c r="K548" s="93">
+        <v>4709000</v>
+      </c>
+      <c r="L548" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M548" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N548" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O548" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P548" s="90">
+        <v>44006127</v>
+      </c>
+      <c r="Q548" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R548" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S548" s="90" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="549" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A549" s="90">
+        <v>333</v>
+      </c>
+      <c r="B549" s="90">
+        <v>442</v>
+      </c>
+      <c r="C549" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D549" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="E549" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F549" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G549" s="92">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="H549" s="93">
+        <v>175104100</v>
+      </c>
+      <c r="I549" s="93">
+        <v>167949100</v>
+      </c>
+      <c r="J549" s="93">
+        <v>1080000</v>
+      </c>
+      <c r="K549" s="93">
+        <v>8235000</v>
+      </c>
+      <c r="L549" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M549" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N549" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O549" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P549" s="90">
+        <v>1036606819</v>
+      </c>
+      <c r="Q549" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R549" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S549" s="90" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="550" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A550" s="90">
+        <v>395</v>
+      </c>
+      <c r="B550" s="90">
+        <v>1528</v>
+      </c>
+      <c r="C550" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D550" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E550" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F550" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G550" s="92">
+        <v>0.39652777777777776</v>
+      </c>
+      <c r="H550" s="93">
+        <v>207247050</v>
+      </c>
+      <c r="I550" s="93">
+        <v>194848050</v>
+      </c>
+      <c r="J550" s="93">
+        <v>1300000</v>
+      </c>
+      <c r="K550" s="93">
+        <v>13699000</v>
+      </c>
+      <c r="L550" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M550" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N550" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O550" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P550" s="90">
+        <v>1121857901</v>
+      </c>
+      <c r="Q550" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R550" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S550" s="90" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="551" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A551" s="90">
+        <v>292</v>
+      </c>
+      <c r="B551" s="90">
+        <v>5116</v>
+      </c>
+      <c r="C551" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D551" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E551" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F551" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G551" s="92">
+        <v>0.43263888888888891</v>
+      </c>
+      <c r="H551" s="93">
+        <v>133941700</v>
+      </c>
+      <c r="I551" s="93">
+        <v>117836700</v>
+      </c>
+      <c r="J551" s="93">
+        <v>14450000</v>
+      </c>
+      <c r="K551" s="93">
+        <v>30555000</v>
+      </c>
+      <c r="L551" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M551" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N551" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O551" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P551" s="90">
+        <v>44006127</v>
+      </c>
+      <c r="Q551" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R551" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S551" s="90" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="552" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A552" s="90">
+        <v>420</v>
+      </c>
+      <c r="B552" s="90">
+        <v>5173</v>
+      </c>
+      <c r="C552" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D552" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E552" s="91">
+        <v>46099</v>
+      </c>
+      <c r="F552" s="91">
+        <v>46098</v>
+      </c>
+      <c r="G552" s="92">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="H552" s="93">
+        <v>79545200</v>
+      </c>
+      <c r="I552" s="93">
+        <v>79725200</v>
+      </c>
+      <c r="J552" s="93">
+        <v>180000</v>
+      </c>
+      <c r="K552" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="L552" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="M552" s="90" t="s">
+        <v>958</v>
+      </c>
+      <c r="N552" s="90" t="s">
+        <v>963</v>
+      </c>
+      <c r="O552" s="90" t="s">
+        <v>590</v>
+      </c>
+      <c r="P552" s="90">
+        <v>1020436470</v>
+      </c>
+      <c r="Q552" s="90" t="s">
+        <v>960</v>
+      </c>
+      <c r="R552" s="90" t="s">
+        <v>965</v>
+      </c>
+      <c r="S552" s="90" t="s">
+        <v>590</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P510" xr:uid="{4CA7671C-9926-4D00-BFA4-A7B2406C1955}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="907"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P510" xr:uid="{4CA7671C-9926-4D00-BFA4-A7B2406C1955}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P191">
     <sortCondition ref="A2:A191"/>
     <sortCondition ref="B2:B191"/>
@@ -52839,7 +55375,7 @@
   <conditionalFormatting sqref="B2:B188">
     <cfRule type="duplicateValues" dxfId="10" priority="190"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B1048576">
+  <conditionalFormatting sqref="B2:B510 B553:B1048576">
     <cfRule type="duplicateValues" dxfId="9" priority="21"/>
     <cfRule type="duplicateValues" dxfId="8" priority="23"/>
     <cfRule type="duplicateValues" dxfId="7" priority="24"/>
